--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>44459</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28147-2022</t>
+          <t>A 27395-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>46189</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -872,23 +872,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -900,18 +905,134 @@
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
       <c r="T4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" t="n">
+        <v>16</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Entita
+Grantaggsvamp
+Talltita
+Vedticka
+Spillkråka
+Tofsmes
+Smålom</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28147-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
         <v>15</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>14</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre hackspett
@@ -923,157 +1044,36 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 27395-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16</v>
-      </c>
-      <c r="U5" t="n">
-        <v>16</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Entita
-Grantaggsvamp
-Talltita
-Vedticka
-Spillkråka
-Tofsmes
-Smålom</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
         <v/>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         <v>45566</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46174</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>45517</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45368</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44539</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35099-2025</t>
+          <t>A 11637-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2081,14 +2081,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45852</v>
+        <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,17 +2102,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>16.5</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2130,808 +2130,808 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 35099-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 11278-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>12</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Entita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 15523-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46106</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>3.7</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Thymalus limbatus
 Vanlig flatbagge</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 27240-2026</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>46184</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.9</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Skogsödla</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 37012-2022</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>44806</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>3.9</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>10</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S 765-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 11637-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S 765-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Rävticka</t>
-        </is>
-      </c>
       <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/S 765-2025 artfynd.xlsx", "S 765-2025")</f>
         <v/>
@@ -2981,7 +2981,7 @@
         <v>46052</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45393</v>
+        <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3241,46 +3241,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45127</v>
+        <v>45447</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3343,49 +3343,53 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12550-2026</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>45559</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3414,23 +3418,18 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3444,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3456,46 +3455,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12557-2026</t>
+          <t>A 12550-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3512,7 +3511,7 @@
         <v>46090</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,13 +3529,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3566,46 +3565,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 12557-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3619,10 +3618,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45305</v>
+        <v>46090</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3634,14 +3633,19 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3671,50 +3675,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45559</v>
+        <v>45362</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,16 +3744,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3780,39 +3780,43 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
@@ -3836,7 +3840,7 @@
         <v>45918</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3924,7 +3928,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3938,10 +3942,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45042</v>
+        <v>45393</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3954,7 +3958,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3990,46 +3994,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4043,10 +4047,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45447</v>
+        <v>45127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4092,53 +4096,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 290-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45362</v>
+        <v>45656</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4208,46 +4208,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 290-2025</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4261,10 +4257,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45656</v>
+        <v>45305</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4277,13 +4273,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4317,35 +4313,39 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46052</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44601</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44656</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44510</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44519</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44830</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44734</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44609</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>44632</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44488</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>44748</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44843</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44609</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45483</v>
+        <v>44589</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6120,7 +6120,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44839</v>
+        <v>44824</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45553</v>
+        <v>44916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6222,13 +6222,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6271,7 +6266,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6285,10 +6280,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45093</v>
+        <v>44937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6301,7 +6296,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6361,7 +6356,7 @@
         <v>45373</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6412,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6431,10 +6426,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45056</v>
+        <v>44479</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6447,7 +6442,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6490,7 +6485,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6500,14 +6495,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45250</v>
+        <v>45093</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6520,7 +6515,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6563,7 +6558,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6577,10 +6572,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45397</v>
+        <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6593,7 +6588,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6636,7 +6631,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6650,10 +6645,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45263</v>
+        <v>45540</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6666,7 +6661,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6709,7 +6704,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6719,14 +6714,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45334</v>
+        <v>45231</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6739,7 +6734,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6782,7 +6777,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6796,10 +6791,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44484</v>
+        <v>45553</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6811,8 +6806,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45043</v>
+        <v>45622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6928,7 +6928,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44589</v>
+        <v>45438</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45670</v>
+        <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7030,13 +7030,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>18.8</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7079,7 +7074,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 10274-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7093,10 +7088,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45666</v>
+        <v>44986</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7109,7 +7104,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7152,7 +7147,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 58548-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45231</v>
+        <v>45635</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7182,7 +7177,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7225,7 +7220,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45134</v>
+        <v>46009</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7254,8 +7249,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7298,7 +7298,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45554</v>
+        <v>46009</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7327,8 +7327,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7371,7 +7376,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7385,10 +7390,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45047</v>
+        <v>46009</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7400,8 +7405,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7444,7 +7454,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7458,10 +7468,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45740</v>
+        <v>45559</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7474,7 +7484,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7517,7 +7527,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7527,14 +7537,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45068</v>
+        <v>45309</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7547,7 +7557,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7590,7 +7600,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 26863-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7604,10 +7614,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45112</v>
+        <v>45810</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7619,13 +7629,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7668,7 +7673,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7678,14 +7683,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45112</v>
+        <v>46031</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7697,13 +7702,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7746,7 +7746,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11794-2023</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44994</v>
+        <v>45134</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7819,7 +7819,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44950</v>
+        <v>45163</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7892,7 +7892,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45911</v>
+        <v>45421</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46073</v>
+        <v>45911</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8038,7 +8038,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51659-2021</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44462</v>
+        <v>46055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8111,7 +8111,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45236</v>
+        <v>45730</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8140,8 +8140,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8184,7 +8189,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8198,10 +8203,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45001</v>
+        <v>45241</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8214,7 +8219,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8257,7 +8262,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8271,10 +8276,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45113</v>
+        <v>46073</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8287,7 +8292,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8330,7 +8335,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8344,10 +8349,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44993</v>
+        <v>45539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8360,7 +8365,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8403,7 +8408,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8417,10 +8422,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44916</v>
+        <v>44965</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8433,7 +8438,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8476,7 +8481,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8490,10 +8495,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45553</v>
+        <v>46090</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8511,7 +8516,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8554,7 +8559,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8564,14 +8569,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45204</v>
+        <v>45740</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8584,7 +8589,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8627,7 +8632,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8641,10 +8646,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45163</v>
+        <v>45047</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8657,7 +8662,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8700,7 +8705,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46090</v>
+        <v>45047</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8729,13 +8734,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8795,7 +8795,7 @@
         <v>46090</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8866,14 +8866,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44796</v>
+        <v>44986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>12.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8929,7 +8929,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46101</v>
+        <v>45091</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9002,7 +9002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45085</v>
+        <v>45337</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44824</v>
+        <v>46101</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9148,7 +9148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44748</v>
+        <v>45672</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45127</v>
+        <v>46126</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9294,7 +9294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45973</v>
+        <v>45068</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9323,13 +9323,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9372,7 +9367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9386,10 +9381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45270</v>
+        <v>45068</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9402,7 +9397,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9445,7 +9440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45539</v>
+        <v>45973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9474,8 +9469,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46126</v>
+        <v>45670</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9547,8 +9547,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>18.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9591,7 +9596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9605,10 +9610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44479</v>
+        <v>45840</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9621,7 +9626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9664,7 +9669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9678,10 +9683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45553</v>
+        <v>44839</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9693,13 +9698,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9742,7 +9742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 11794-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46002</v>
+        <v>44994</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46002</v>
+        <v>45098</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9888,7 +9888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45840</v>
+        <v>45128</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9961,7 +9961,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9975,10 +9975,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45740</v>
+        <v>45128</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10034,7 +10034,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10044,14 +10044,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46009</v>
+        <v>45250</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10063,13 +10063,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10112,7 +10107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10126,10 +10121,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45559</v>
+        <v>45270</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10142,7 +10137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10185,7 +10180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10199,10 +10194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10214,13 +10209,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10263,7 +10253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10277,10 +10267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10292,13 +10282,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10341,7 +10326,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10355,10 +10340,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45128</v>
+        <v>44484</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10371,7 +10356,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10414,7 +10399,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 51659-2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10428,10 +10413,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45128</v>
+        <v>44462</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10444,7 +10429,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10487,7 +10472,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10501,10 +10486,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46031</v>
+        <v>45560</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10517,7 +10502,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>12</v>
+        <v>0.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10560,7 +10545,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10574,10 +10559,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45098</v>
+        <v>45342</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10590,7 +10575,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10633,7 +10618,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10647,10 +10632,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45153</v>
+        <v>44998</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10662,13 +10647,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10711,7 +10691,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10721,14 +10701,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46055</v>
+        <v>45068</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10741,7 +10721,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10784,7 +10764,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10798,10 +10778,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44589</v>
+        <v>45174</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10813,8 +10793,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10857,7 +10842,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10871,10 +10856,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45163</v>
+        <v>44848</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10887,7 +10872,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10930,7 +10915,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10944,10 +10929,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44965</v>
+        <v>45236</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10960,7 +10945,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11003,7 +10988,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11017,10 +11002,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45342</v>
+        <v>45769</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11033,7 +11018,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11076,7 +11061,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11090,10 +11075,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45047</v>
+        <v>46155</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11105,8 +11090,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.3</v>
+        <v>7.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11149,7 +11139,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11159,14 +11149,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44989</v>
+        <v>46167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11179,7 +11169,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11222,7 +11212,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11239,7 +11229,7 @@
         <v>44989</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11252,7 +11242,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11295,7 +11285,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11305,14 +11295,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46155</v>
+        <v>44989</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11324,13 +11314,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11373,7 +11358,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 47902-2023</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11387,10 +11372,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45204</v>
+        <v>46174</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11403,7 +11388,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11446,7 +11431,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11460,10 +11445,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44804</v>
+        <v>46174</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11476,7 +11461,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11519,7 +11504,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11533,10 +11518,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45769</v>
+        <v>45813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11549,7 +11534,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11592,7 +11577,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11606,10 +11591,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44712</v>
+        <v>46182</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11622,7 +11607,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11665,7 +11650,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11679,10 +11664,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45093</v>
+        <v>46190</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11694,8 +11679,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11738,7 +11728,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11752,10 +11742,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44624</v>
+        <v>46189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11767,8 +11757,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>7.9</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11811,7 +11806,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11825,10 +11820,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45069</v>
+        <v>46189</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11840,8 +11835,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46167</v>
+        <v>46190</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11913,8 +11913,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11957,7 +11962,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11971,10 +11976,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44848</v>
+        <v>46189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11984,6 +11989,11 @@
       <c r="G138" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -12030,7 +12040,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12044,10 +12054,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44676</v>
+        <v>46189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12059,8 +12069,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12103,7 +12118,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12117,10 +12132,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45813</v>
+        <v>46189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12133,7 +12148,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>10.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12176,7 +12191,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12190,10 +12205,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46174</v>
+        <v>46189</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12205,8 +12220,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12249,7 +12269,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12263,10 +12283,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46174</v>
+        <v>46191</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12278,8 +12298,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.3</v>
+        <v>7.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12322,7 +12347,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12336,10 +12361,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45421</v>
+        <v>46195</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12351,8 +12376,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12395,7 +12425,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12409,10 +12439,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45438</v>
+        <v>46197</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12425,7 +12455,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12468,7 +12498,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12482,10 +12512,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46182</v>
+        <v>46197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12498,7 +12528,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12541,7 +12571,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12555,10 +12585,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45730</v>
+        <v>44950</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12570,13 +12600,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12619,7 +12644,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12633,10 +12658,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44764</v>
+        <v>46199</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12648,8 +12673,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>9.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12692,7 +12722,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12706,10 +12736,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12727,7 +12757,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12770,7 +12800,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12784,10 +12814,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12805,7 +12835,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12848,7 +12878,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12862,10 +12892,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45337</v>
+        <v>45001</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12878,7 +12908,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12921,7 +12951,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12935,10 +12965,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46189</v>
+        <v>46244</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12956,7 +12986,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12999,7 +13029,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13013,10 +13043,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46189</v>
+        <v>46202</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13028,8 +13058,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>10.7</v>
+        <v>4.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13072,7 +13107,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13086,10 +13121,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45421</v>
+        <v>45397</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13102,7 +13137,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13145,7 +13180,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13159,10 +13194,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46189</v>
+        <v>46256</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13180,7 +13215,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13223,7 +13258,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13237,10 +13272,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46189</v>
+        <v>46256</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13258,7 +13293,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13301,7 +13336,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13315,10 +13350,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46191</v>
+        <v>44764</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13330,13 +13365,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13379,7 +13409,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13389,14 +13419,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46190</v>
+        <v>46256</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13414,7 +13444,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13457,7 +13487,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13467,14 +13497,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46190</v>
+        <v>46256</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13492,7 +13522,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13535,7 +13565,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13549,10 +13579,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46195</v>
+        <v>46219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13564,13 +13594,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13613,7 +13638,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13627,10 +13652,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45540</v>
+        <v>46219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13643,7 +13668,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13686,7 +13711,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13700,10 +13725,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46197</v>
+        <v>46219</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13716,7 +13741,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13759,7 +13784,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13773,10 +13798,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45523</v>
+        <v>46222</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13789,7 +13814,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13832,7 +13857,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13846,10 +13871,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45523</v>
+        <v>45331</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13862,7 +13887,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13905,7 +13930,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13919,10 +13944,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46197</v>
+        <v>46273</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13934,8 +13959,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13978,7 +14008,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13992,10 +14022,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14013,7 +14043,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14056,7 +14086,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14070,10 +14100,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45331</v>
+        <v>46273</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14085,8 +14115,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14129,7 +14164,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14143,10 +14178,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44998</v>
+        <v>46273</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14158,8 +14193,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14202,7 +14242,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14216,10 +14256,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14237,7 +14277,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14280,7 +14320,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14294,10 +14334,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14315,7 +14355,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14358,7 +14398,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14372,10 +14412,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44950</v>
+        <v>46273</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14387,8 +14427,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14431,7 +14476,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14445,10 +14490,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46244</v>
+        <v>46273</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14466,7 +14511,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14509,7 +14554,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14523,10 +14568,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44992</v>
+        <v>46230</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14538,13 +14583,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14587,7 +14627,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14601,10 +14641,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46202</v>
+        <v>46273</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14622,7 +14662,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14665,7 +14705,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 36996-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14679,10 +14719,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45056</v>
+        <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14694,8 +14734,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14738,7 +14783,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 36997-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14752,10 +14797,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44937</v>
+        <v>46273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14767,8 +14812,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14811,7 +14861,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14825,10 +14875,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45281</v>
+        <v>46273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14840,8 +14890,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14884,7 +14939,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14898,10 +14953,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45560</v>
+        <v>46230</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14914,7 +14969,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14957,7 +15012,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14971,10 +15026,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45091</v>
+        <v>46273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14986,8 +15041,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15030,7 +15090,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15044,10 +15104,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45001</v>
+        <v>46273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15059,8 +15119,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15103,7 +15168,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15113,14 +15178,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46256</v>
+        <v>46274</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15132,13 +15197,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15181,7 +15241,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15191,14 +15251,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46256</v>
+        <v>45112</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15212,11 +15272,11 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15259,7 +15319,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15273,10 +15333,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46256</v>
+        <v>45014</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15288,13 +15348,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>4.8</v>
+        <v>12.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15337,7 +15392,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15351,10 +15406,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46256</v>
+        <v>45263</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15366,13 +15421,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15415,7 +15465,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15429,10 +15479,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44988</v>
+        <v>45421</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15444,13 +15494,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15493,7 +15538,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15503,14 +15548,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45309</v>
+        <v>45204</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15523,7 +15568,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15566,7 +15611,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15580,10 +15625,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46219</v>
+        <v>45740</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15596,7 +15641,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15639,7 +15684,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15653,10 +15698,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46219</v>
+        <v>45085</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15669,7 +15714,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15712,7 +15757,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15726,10 +15771,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45762</v>
+        <v>45056</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15742,7 +15787,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15785,7 +15830,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15799,10 +15844,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45553</v>
+        <v>45127</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15814,13 +15859,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15863,7 +15903,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15877,10 +15917,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45553</v>
+        <v>44993</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15892,13 +15932,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15941,7 +15976,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 47902-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15955,10 +15990,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46219</v>
+        <v>45204</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15971,7 +16006,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16014,7 +16049,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16028,10 +16063,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45241</v>
+        <v>45093</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16044,7 +16079,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16087,7 +16122,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16101,10 +16136,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45014</v>
+        <v>45281</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16117,7 +16152,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>12.1</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16160,7 +16195,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16174,10 +16209,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45068</v>
+        <v>44676</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16190,7 +16225,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16233,7 +16268,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16247,10 +16282,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45068</v>
+        <v>44624</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16263,7 +16298,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>7.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16306,7 +16341,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16320,10 +16355,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46222</v>
+        <v>45554</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16336,7 +16371,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16379,7 +16414,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16393,10 +16428,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45616</v>
+        <v>45523</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16409,7 +16444,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16452,7 +16487,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16466,10 +16501,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46273</v>
+        <v>45523</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16479,11 +16514,6 @@
       <c r="G198" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I198" t="n">
@@ -16530,7 +16560,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16544,10 +16574,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46273</v>
+        <v>45153</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16565,7 +16595,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16608,7 +16638,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16622,10 +16652,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46273</v>
+        <v>45666</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16637,13 +16667,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16686,7 +16711,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16700,10 +16725,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46273</v>
+        <v>45113</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16715,13 +16740,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16764,7 +16784,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16778,10 +16798,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46273</v>
+        <v>44992</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16799,7 +16819,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16842,7 +16862,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16856,10 +16876,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46273</v>
+        <v>44712</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16871,13 +16891,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16920,7 +16935,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16934,10 +16949,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46274</v>
+        <v>45616</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16950,7 +16965,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16993,7 +17008,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17007,10 +17022,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46230</v>
+        <v>45553</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17022,8 +17037,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17066,7 +17086,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17076,14 +17096,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44986</v>
+        <v>45043</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17096,7 +17116,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17139,7 +17159,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17153,10 +17173,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46273</v>
+        <v>45483</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17168,13 +17188,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17217,7 +17232,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17231,10 +17246,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46273</v>
+        <v>44988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17252,7 +17267,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17295,7 +17310,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17309,10 +17324,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46230</v>
+        <v>44804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17325,7 +17340,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17368,7 +17383,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17382,10 +17397,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46273</v>
+        <v>45069</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17397,13 +17412,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17446,7 +17456,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17460,10 +17470,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46273</v>
+        <v>45163</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17475,13 +17485,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17524,7 +17529,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17538,10 +17543,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46273</v>
+        <v>45762</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17553,13 +17558,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17602,7 +17602,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 36996-2026</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17616,10 +17616,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46273</v>
+        <v>45056</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17631,13 +17631,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17680,7 +17675,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36997-2026</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17694,10 +17689,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17715,7 +17710,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17758,7 +17753,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17772,10 +17767,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17793,7 +17788,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17836,7 +17831,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17850,10 +17845,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45601</v>
+        <v>45646</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17866,7 +17861,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17909,7 +17904,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17919,14 +17914,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45174</v>
+        <v>45334</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17938,13 +17933,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17987,7 +17977,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18001,10 +17991,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45672</v>
+        <v>44950</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18017,7 +18007,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18060,7 +18050,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18074,10 +18064,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45646</v>
+        <v>45601</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18090,7 +18080,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18133,7 +18123,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61470-2024</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18147,10 +18137,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45646</v>
+        <v>44589</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18163,7 +18153,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18206,7 +18196,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18220,10 +18210,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45656</v>
+        <v>44748</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18236,7 +18226,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18279,7 +18269,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18289,14 +18279,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45600</v>
+        <v>45112</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18308,8 +18298,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18352,7 +18347,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 33334-2023</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18366,10 +18361,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45128</v>
+        <v>45553</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18381,8 +18376,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18425,7 +18425,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 61470-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18439,10 +18439,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45670</v>
+        <v>45646</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18454,13 +18454,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18503,7 +18498,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18517,10 +18512,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45622</v>
+        <v>45670</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18532,8 +18527,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>2.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18576,7 +18576,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 10274-2023</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18590,10 +18590,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44986</v>
+        <v>45656</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18649,7 +18649,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 58548-2024</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18663,10 +18663,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45635</v>
+        <v>45600</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 26863-2025</t>
+          <t>A 33334-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18736,10 +18736,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45810</v>
+        <v>45128</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18812,7 +18812,7 @@
         <v>44889</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44889</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>46256</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>44459</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28147-2022</t>
+          <t>A 27395-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>46189</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -872,23 +872,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -900,18 +905,134 @@
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
       <c r="T4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" t="n">
+        <v>16</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Entita
+Grantaggsvamp
+Talltita
+Vedticka
+Spillkråka
+Tofsmes
+Smålom</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28147-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
         <v>15</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>14</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre hackspett
@@ -923,157 +1044,36 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 27395-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16</v>
-      </c>
-      <c r="U5" t="n">
-        <v>16</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Entita
-Grantaggsvamp
-Talltita
-Vedticka
-Spillkråka
-Tofsmes
-Smålom</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
         <v/>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         <v>45566</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46174</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33104-2024</t>
+          <t>A 31357-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45517</v>
+        <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1552,45 +1552,157 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka
+Tjäder
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 31357-2026 artfynd.xlsx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 31357-2026 karta.png", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 31357-2026 georefererad karta.tif", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 31357-2026 FSC-klagomål.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 31357-2026 FSC-klagomål mail.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 31357-2026 tillsynsbegäran.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 31357-2026 tillsynsbegäran mail.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 31357-2026 prioriterade fågelarter.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 33104-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45517</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blekspindling agg.
@@ -1598,155 +1710,43 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33104-2024 artfynd.xlsx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33104-2024 karta.png", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33104-2024 georefererad karta.tif", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 33104-2024 karta knärot.png", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33104-2024 FSC-klagomål.docx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33104-2024 FSC-klagomål mail.docx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33104-2024 tillsynsbegäran.docx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33104-2024 tillsynsbegäran mail.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31357-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>11</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka
-Tjäder
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 31357-2026 artfynd.xlsx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 31357-2026 karta.png", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 31357-2026 georefererad karta.tif", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 31357-2026 FSC-klagomål.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 31357-2026 FSC-klagomål mail.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 31357-2026 tillsynsbegäran.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 31357-2026 tillsynsbegäran mail.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 31357-2026 prioriterade fågelarter.docx", "A 31357-2026")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 10680-2024</t>
+          <t>A 58428-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45368</v>
+        <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1800,160 +1800,160 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Bågpraktmossa
+Hässleklocka
+Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 58428-2025 artfynd.xlsx", "A 58428-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 58428-2025 karta.png", "A 58428-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 58428-2025 georefererad karta.tif", "A 58428-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 58428-2025 FSC-klagomål.docx", "A 58428-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 58428-2025 FSC-klagomål mail.docx", "A 58428-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 58428-2025 tillsynsbegäran.docx", "A 58428-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 58428-2025 tillsynsbegäran mail.docx", "A 58428-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 10680-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45368</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Ask
 Svinrot
 Blåsippa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 10680-2024 artfynd.xlsx", "A 10680-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 10680-2024 karta.png", "A 10680-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 10680-2024 georefererad karta.tif", "A 10680-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 10680-2024 FSC-klagomål.docx", "A 10680-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 10680-2024 FSC-klagomål mail.docx", "A 10680-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 10680-2024 tillsynsbegäran.docx", "A 10680-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 10680-2024 tillsynsbegäran mail.docx", "A 10680-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58428-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Bågpraktmossa
-Hässleklocka
-Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 58428-2025 artfynd.xlsx", "A 58428-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 58428-2025 karta.png", "A 58428-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 58428-2025 georefererad karta.tif", "A 58428-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 58428-2025 FSC-klagomål.docx", "A 58428-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 58428-2025 FSC-klagomål mail.docx", "A 58428-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 58428-2025 tillsynsbegäran.docx", "A 58428-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 58428-2025 tillsynsbegäran mail.docx", "A 58428-2025")</f>
         <v/>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         <v>44539</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37012-2022</t>
+          <t>A 11637-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2081,14 +2081,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44806</v>
+        <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2100,23 +2100,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2134,804 +2139,799 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 35099-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 11278-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 15523-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Thymalus limbatus
+Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 37012-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44806</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
         <v>10</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 11278-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46080</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S 765-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 15523-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Thymalus limbatus
-Vanlig flatbagge</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 27240-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 11637-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 35099-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45852</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S 765-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Rävticka</t>
-        </is>
-      </c>
       <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/S 765-2025 artfynd.xlsx", "S 765-2025")</f>
         <v/>
@@ -2981,7 +2981,7 @@
         <v>46052</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45393</v>
+        <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3241,46 +3241,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45127</v>
+        <v>45447</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3343,42 +3343,46 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
@@ -3402,7 +3406,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3512,7 +3516,7 @@
         <v>46090</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3605,7 +3609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3619,10 +3623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45042</v>
+        <v>45559</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,17 +3639,17 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3659,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3671,46 +3675,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3724,10 +3728,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45559</v>
+        <v>45362</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3740,16 +3744,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3764,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3776,46 +3780,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3829,10 +3837,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45447</v>
+        <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3845,7 +3853,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3878,46 +3886,42 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
@@ -3941,7 +3945,7 @@
         <v>45918</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4029,7 +4033,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4043,10 +4047,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45305</v>
+        <v>45127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4095,50 +4099,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 290-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45362</v>
+        <v>45656</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4208,46 +4208,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 290-2025</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4261,10 +4257,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45656</v>
+        <v>45305</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4277,13 +4273,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4317,35 +4313,39 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46052</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44601</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44656</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44510</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44519</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44830</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44734</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44609</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>44632</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44488</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5043-2022</t>
+          <t>A 28616-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44593</v>
+        <v>44748</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45105-2022</t>
+          <t>A 5043-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44843</v>
+        <v>44593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28616-2022</t>
+          <t>A 45105-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5764,10 +5764,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44748</v>
+        <v>44843</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5823,7 +5823,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 8050-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5837,10 +5837,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44839</v>
+        <v>44609</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5896,7 +5896,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8050-2022</t>
+          <t>A 67508-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5910,10 +5910,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44609</v>
+        <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5969,7 +5969,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 41979-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45421</v>
+        <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5998,8 +5998,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6042,7 +6047,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45553</v>
+        <v>44589</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6071,13 +6076,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6120,7 +6120,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45093</v>
+        <v>44824</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 67508-2021</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44524</v>
+        <v>44916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41979-2022</t>
+          <t>A 11676-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44830</v>
+        <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6295,13 +6295,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6344,7 +6339,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6358,10 +6353,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45483</v>
+        <v>44479</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6374,7 +6369,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6417,7 +6412,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11676-2024</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6431,10 +6426,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45373</v>
+        <v>44937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6447,7 +6442,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6490,7 +6485,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6504,10 +6499,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45056</v>
+        <v>44796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6520,7 +6515,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6563,7 +6558,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6577,10 +6572,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45438</v>
+        <v>45093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6593,7 +6588,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6636,7 +6631,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6646,14 +6641,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45250</v>
+        <v>45231</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6666,7 +6661,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6709,7 +6704,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6723,10 +6718,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45397</v>
+        <v>45540</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6739,7 +6734,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6782,7 +6777,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6796,10 +6791,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45730</v>
+        <v>45553</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6813,11 +6808,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6860,7 +6855,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6874,10 +6869,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44764</v>
+        <v>45438</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6890,7 +6885,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.300000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6933,7 +6928,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6947,10 +6942,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45337</v>
+        <v>45001</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6963,7 +6958,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7006,7 +7001,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7020,10 +7015,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45421</v>
+        <v>45134</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7036,7 +7031,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7079,7 +7074,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7093,10 +7088,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45263</v>
+        <v>45309</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7109,7 +7104,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7152,7 +7147,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45134</v>
+        <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7182,7 +7177,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7225,7 +7220,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45740</v>
+        <v>45421</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7255,7 +7250,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7298,7 +7293,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7312,10 +7307,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46090</v>
+        <v>46031</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7327,13 +7322,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7376,7 +7366,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 26863-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7386,14 +7376,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45334</v>
+        <v>45810</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7406,7 +7396,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7449,7 +7439,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12547-2026</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7463,10 +7453,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46090</v>
+        <v>45730</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7480,11 +7470,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7527,7 +7517,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7541,10 +7531,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45043</v>
+        <v>45241</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7557,7 +7547,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7600,7 +7590,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7614,10 +7604,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44589</v>
+        <v>45911</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7630,7 +7620,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7673,7 +7663,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7687,10 +7677,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44484</v>
+        <v>45539</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7703,7 +7693,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7746,7 +7736,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7760,10 +7750,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46101</v>
+        <v>44965</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7776,7 +7766,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7819,7 +7809,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7833,10 +7823,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45911</v>
+        <v>45047</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7849,7 +7839,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7892,7 +7882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7906,10 +7896,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45670</v>
+        <v>45047</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7921,13 +7911,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>18.8</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7970,7 +7955,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7980,14 +7965,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45666</v>
+        <v>44986</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8000,7 +7985,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8043,7 +8028,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8057,10 +8042,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45231</v>
+        <v>45091</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8073,7 +8058,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.7</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8116,7 +8101,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8130,10 +8115,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45554</v>
+        <v>45740</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8146,7 +8131,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8189,7 +8174,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8203,10 +8188,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45540</v>
+        <v>45337</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8219,7 +8204,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8262,7 +8247,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8276,10 +8261,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45047</v>
+        <v>46055</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8292,7 +8277,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8335,7 +8320,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8349,10 +8334,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46126</v>
+        <v>45672</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8408,7 +8393,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8422,10 +8407,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45523</v>
+        <v>45068</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8438,7 +8423,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8481,7 +8466,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8495,10 +8480,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45523</v>
+        <v>45068</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8511,7 +8496,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8554,7 +8539,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8568,10 +8553,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45840</v>
+        <v>45973</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8583,8 +8568,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8627,7 +8617,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8641,10 +8631,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45331</v>
+        <v>45670</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8656,8 +8646,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>5.8</v>
+        <v>18.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8700,7 +8695,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8710,14 +8705,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45068</v>
+        <v>44839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8730,7 +8725,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8773,7 +8768,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 11794-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8787,10 +8782,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44998</v>
+        <v>44994</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8803,7 +8798,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8846,7 +8841,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8860,10 +8855,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45112</v>
+        <v>46073</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8875,13 +8870,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8924,7 +8914,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8934,14 +8924,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45112</v>
+        <v>45098</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8953,13 +8943,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9002,7 +8987,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11794-2023</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9016,10 +9001,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44994</v>
+        <v>45128</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9032,7 +9017,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9075,7 +9060,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9089,10 +9074,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44950</v>
+        <v>45128</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9105,7 +9090,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9148,7 +9133,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 51659-2021</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9158,14 +9143,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44462</v>
+        <v>45250</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9178,7 +9163,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9221,7 +9206,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9235,10 +9220,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45973</v>
+        <v>45270</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9250,13 +9235,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9299,7 +9279,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9313,10 +9293,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45236</v>
+        <v>44484</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9329,7 +9309,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9372,7 +9352,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9386,10 +9366,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45001</v>
+        <v>46090</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9401,8 +9381,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9445,7 +9430,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 51659-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9459,10 +9444,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44950</v>
+        <v>44462</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9475,7 +9460,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9518,7 +9503,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9532,10 +9517,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45113</v>
+        <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9548,7 +9533,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9591,7 +9576,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9605,10 +9590,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44992</v>
+        <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9620,13 +9605,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9669,7 +9649,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 12547-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9683,10 +9663,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44993</v>
+        <v>46090</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9698,8 +9678,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9742,7 +9727,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9756,10 +9741,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45056</v>
+        <v>45560</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9772,7 +9757,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9815,7 +9800,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9829,10 +9814,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44916</v>
+        <v>45342</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9845,7 +9830,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9888,7 +9873,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9902,10 +9887,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45553</v>
+        <v>46009</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9919,11 +9904,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9966,7 +9951,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9976,14 +9961,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45204</v>
+        <v>46009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9995,8 +9980,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10039,7 +10029,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10053,10 +10043,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45163</v>
+        <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10068,8 +10058,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10112,7 +10107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10126,10 +10121,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44937</v>
+        <v>45559</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10142,7 +10137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10185,7 +10180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10199,10 +10194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44796</v>
+        <v>44998</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10215,7 +10210,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10258,7 +10253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10272,10 +10267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45085</v>
+        <v>46101</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10288,7 +10283,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10331,7 +10326,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10341,14 +10336,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46002</v>
+        <v>45068</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10361,7 +10356,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10404,7 +10399,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10418,10 +10413,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44824</v>
+        <v>45174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10433,8 +10428,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44748</v>
+        <v>44848</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10550,7 +10550,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>45236</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10623,7 +10623,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10633,14 +10633,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46009</v>
+        <v>44989</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10652,13 +10652,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10701,7 +10696,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10711,14 +10706,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46155</v>
+        <v>44989</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10730,13 +10725,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10779,7 +10769,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10793,10 +10783,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45559</v>
+        <v>46126</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10809,7 +10799,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10852,7 +10842,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10866,10 +10856,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46009</v>
+        <v>44950</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10881,13 +10871,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10930,7 +10915,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10944,10 +10929,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45769</v>
+        <v>45001</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10960,7 +10945,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11003,7 +10988,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11017,10 +11002,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46009</v>
+        <v>45397</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11032,13 +11017,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11081,7 +11061,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11095,10 +11075,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45127</v>
+        <v>45840</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11111,7 +11091,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11154,7 +11134,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11168,10 +11148,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45281</v>
+        <v>44764</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11184,7 +11164,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11227,7 +11207,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11241,10 +11221,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45270</v>
+        <v>45331</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11257,7 +11237,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11300,7 +11280,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11314,10 +11294,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45539</v>
+        <v>45112</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11329,8 +11309,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11373,7 +11358,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11387,10 +11372,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46031</v>
+        <v>45014</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11403,7 +11388,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11446,7 +11431,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11460,10 +11445,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46167</v>
+        <v>45263</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11476,7 +11461,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11519,7 +11504,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11533,10 +11518,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44479</v>
+        <v>45421</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11549,7 +11534,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11592,7 +11577,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11602,14 +11587,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45560</v>
+        <v>45204</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11622,7 +11607,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11665,7 +11650,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11679,10 +11664,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45091</v>
+        <v>45769</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11695,7 +11680,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11738,7 +11723,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11752,10 +11737,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45813</v>
+        <v>45740</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11768,7 +11753,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11811,7 +11796,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11825,10 +11810,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46174</v>
+        <v>46155</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11840,8 +11825,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11884,7 +11874,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11898,10 +11888,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46174</v>
+        <v>45085</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11914,7 +11904,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11957,7 +11947,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11971,10 +11961,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45553</v>
+        <v>45056</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11986,13 +11976,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12035,7 +12020,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12049,10 +12034,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45740</v>
+        <v>46167</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12065,7 +12050,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12108,7 +12093,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12122,10 +12107,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46055</v>
+        <v>45127</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12138,7 +12123,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12181,7 +12166,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12195,10 +12180,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45128</v>
+        <v>44993</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12211,7 +12196,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12254,7 +12239,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 47902-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12268,10 +12253,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45128</v>
+        <v>45204</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12284,7 +12269,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12327,7 +12312,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12341,10 +12326,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46182</v>
+        <v>45093</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12357,7 +12342,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12400,7 +12385,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12414,10 +12399,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46189</v>
+        <v>46174</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12429,13 +12414,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12478,7 +12458,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12492,10 +12472,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46189</v>
+        <v>46174</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12507,13 +12487,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12556,7 +12531,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12570,10 +12545,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46073</v>
+        <v>45813</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12586,7 +12561,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12629,7 +12604,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12643,10 +12618,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46189</v>
+        <v>45281</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12658,13 +12633,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12707,7 +12677,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12721,10 +12691,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46189</v>
+        <v>44676</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12737,7 +12707,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>10.7</v>
+        <v>2.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12780,7 +12750,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12794,10 +12764,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45098</v>
+        <v>44624</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12810,7 +12780,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12853,7 +12823,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12867,10 +12837,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46189</v>
+        <v>45554</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12882,13 +12852,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12931,7 +12896,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12945,10 +12910,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46189</v>
+        <v>45523</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12960,13 +12925,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13009,7 +12969,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13023,10 +12983,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45001</v>
+        <v>45523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13039,7 +12999,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13082,7 +13042,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13096,10 +13056,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46191</v>
+        <v>46182</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13111,13 +13071,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13160,7 +13115,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13174,10 +13129,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46190</v>
+        <v>45153</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13195,7 +13150,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13238,7 +13193,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13252,10 +13207,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46190</v>
+        <v>45666</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13267,13 +13222,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13316,7 +13266,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13330,10 +13280,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46195</v>
+        <v>45113</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13345,13 +13295,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13394,7 +13339,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13408,10 +13353,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45153</v>
+        <v>44992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13429,7 +13374,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13472,7 +13417,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13486,10 +13431,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44988</v>
+        <v>44712</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13501,13 +13446,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13550,7 +13490,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13564,10 +13504,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46197</v>
+        <v>46190</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13579,8 +13519,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13623,7 +13568,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13637,10 +13582,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46197</v>
+        <v>46189</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13652,8 +13597,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13696,7 +13646,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13710,10 +13660,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45309</v>
+        <v>46189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13725,8 +13675,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13769,7 +13724,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13783,10 +13738,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46199</v>
+        <v>46190</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13804,7 +13759,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13847,7 +13802,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13861,10 +13816,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44589</v>
+        <v>46189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13876,8 +13831,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13920,7 +13880,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13934,10 +13894,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46199</v>
+        <v>46189</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13955,7 +13915,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13998,7 +13958,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14012,10 +13972,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46199</v>
+        <v>46189</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14027,13 +13987,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>10.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14076,7 +14031,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14090,10 +14045,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45163</v>
+        <v>46189</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14105,8 +14060,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14149,7 +14109,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14163,10 +14123,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46244</v>
+        <v>46191</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14180,11 +14140,11 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14227,7 +14187,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14241,10 +14201,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46202</v>
+        <v>45616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14256,13 +14216,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14305,7 +14260,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14319,10 +14274,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44965</v>
+        <v>46195</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14334,8 +14289,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14378,7 +14338,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14392,10 +14352,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45342</v>
+        <v>45553</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14407,8 +14367,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14451,7 +14416,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14465,10 +14430,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45762</v>
+        <v>45043</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14481,7 +14446,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14524,7 +14489,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14538,10 +14503,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45047</v>
+        <v>45483</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14554,7 +14519,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14597,7 +14562,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14611,10 +14576,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45553</v>
+        <v>44988</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14632,7 +14597,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14675,7 +14640,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14689,10 +14654,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45553</v>
+        <v>44804</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14704,13 +14669,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14753,7 +14713,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14767,10 +14727,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45241</v>
+        <v>46197</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14783,7 +14743,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14826,7 +14786,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14840,10 +14800,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45014</v>
+        <v>46197</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14856,7 +14816,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>12.1</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14899,7 +14859,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14909,14 +14869,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44989</v>
+        <v>46199</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14928,8 +14888,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14972,7 +14937,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14982,14 +14947,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44989</v>
+        <v>46199</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15001,8 +14966,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15045,7 +15015,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15059,10 +15029,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45068</v>
+        <v>46199</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15074,8 +15044,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15118,7 +15093,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15132,10 +15107,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45068</v>
+        <v>46244</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15147,8 +15122,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15191,7 +15171,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47902-2023</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15205,10 +15185,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45204</v>
+        <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15220,8 +15200,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15264,7 +15249,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15278,10 +15263,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44804</v>
+        <v>45069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15294,7 +15279,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15337,7 +15322,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15347,14 +15332,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46256</v>
+        <v>45163</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15366,13 +15351,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15415,7 +15395,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15425,14 +15405,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46256</v>
+        <v>45762</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15444,13 +15424,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15493,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15507,10 +15482,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46256</v>
+        <v>45056</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15522,13 +15497,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15571,7 +15541,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15585,10 +15555,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46256</v>
+        <v>45553</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15606,7 +15576,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15649,7 +15619,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15663,10 +15633,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44712</v>
+        <v>45553</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15678,8 +15648,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15722,7 +15697,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15736,10 +15711,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45093</v>
+        <v>45646</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15752,7 +15727,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15795,7 +15770,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15805,14 +15780,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44624</v>
+        <v>45334</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15825,7 +15800,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15868,7 +15843,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15882,10 +15857,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45069</v>
+        <v>46256</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15897,8 +15872,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15941,7 +15921,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15955,10 +15935,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45616</v>
+        <v>46256</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15970,8 +15950,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16014,7 +15999,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16028,10 +16013,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44848</v>
+        <v>44950</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16044,7 +16029,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16087,7 +16072,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16097,14 +16082,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46219</v>
+        <v>46256</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16116,8 +16101,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16160,7 +16150,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16170,14 +16160,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46219</v>
+        <v>46256</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16189,8 +16179,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16233,7 +16228,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16247,10 +16242,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44676</v>
+        <v>46219</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16263,7 +16258,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16306,7 +16301,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16323,7 +16318,7 @@
         <v>46219</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16336,7 +16331,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16379,7 +16374,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16393,10 +16388,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46222</v>
+        <v>45601</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16409,7 +16404,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16452,7 +16447,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16462,14 +16457,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44986</v>
+        <v>46219</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16482,7 +16477,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>12.8</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16525,7 +16520,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16539,10 +16534,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46273</v>
+        <v>46222</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16554,13 +16549,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16603,7 +16593,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16617,10 +16607,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46273</v>
+        <v>44589</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16632,13 +16622,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16681,7 +16666,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16695,10 +16680,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46273</v>
+        <v>44748</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16710,13 +16695,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16759,7 +16739,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16769,14 +16749,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46273</v>
+        <v>45112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16794,7 +16774,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16837,7 +16817,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16854,7 +16834,7 @@
         <v>46273</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16872,7 +16852,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16915,7 +16895,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16932,7 +16912,7 @@
         <v>46273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16950,7 +16930,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16993,7 +16973,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17007,10 +16987,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17022,8 +17002,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17066,7 +17051,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17080,10 +17065,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46230</v>
+        <v>45553</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17095,8 +17080,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17139,7 +17129,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17156,7 +17146,7 @@
         <v>46273</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17217,7 +17207,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17234,7 +17224,7 @@
         <v>46273</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17252,7 +17242,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17295,7 +17285,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17309,10 +17299,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46230</v>
+        <v>46273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17324,8 +17314,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17368,7 +17363,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17385,7 +17380,7 @@
         <v>46273</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17403,7 +17398,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17446,7 +17441,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17463,7 +17458,7 @@
         <v>46273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17481,7 +17476,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17524,7 +17519,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17538,10 +17533,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46273</v>
+        <v>46230</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17553,13 +17548,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17602,7 +17592,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17616,10 +17606,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45601</v>
+        <v>46273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17631,8 +17621,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17692,7 +17687,7 @@
         <v>46273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17770,7 +17765,7 @@
         <v>46273</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17831,7 +17826,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17848,7 +17843,7 @@
         <v>46273</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17866,7 +17861,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17909,7 +17904,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17923,10 +17918,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45174</v>
+        <v>46230</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17938,13 +17933,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17987,7 +17977,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18001,10 +17991,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45672</v>
+        <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18016,8 +18006,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18060,7 +18055,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 38008-2026</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18074,10 +18069,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18095,7 +18090,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18138,7 +18133,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18152,10 +18147,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45646</v>
+        <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18168,7 +18163,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18228,7 +18223,7 @@
         <v>46280</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18306,7 +18301,7 @@
         <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18362,7 +18357,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 38008-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18376,10 +18371,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45656</v>
+        <v>46280</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18391,8 +18386,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18449,10 +18449,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45600</v>
+        <v>45670</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18464,8 +18464,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18508,7 +18513,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 33334-2023</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18522,10 +18527,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45128</v>
+        <v>45656</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18538,7 +18543,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18581,7 +18586,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18595,10 +18600,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45670</v>
+        <v>45600</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18610,13 +18615,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>9.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18659,7 +18659,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 33334-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18673,10 +18673,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45622</v>
+        <v>45128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18732,7 +18732,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 10274-2023</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18746,10 +18746,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44986</v>
+        <v>45622</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18805,7 +18805,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 58548-2024</t>
+          <t>A 10274-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18819,10 +18819,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45635</v>
+        <v>44986</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 26863-2025</t>
+          <t>A 58548-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18892,10 +18892,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45810</v>
+        <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18968,7 +18968,7 @@
         <v>44889</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>44889</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45317</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45762</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>46030</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46256</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46256</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>44459</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 27395-2026</t>
+          <t>A 28147-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46189</v>
+        <v>44746</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -872,28 +872,23 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -905,18 +900,139 @@
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
       <c r="T4" t="n">
+        <v>15</v>
+      </c>
+      <c r="U4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre hackspett
+Nötkråka
+Ullticka
+Grön sköldmossa
+Hasselsopp
+Stubbspretmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 27395-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
         <v>16</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>16</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Entita
@@ -928,152 +1044,36 @@
 Smålom</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 28147-2022</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>14</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre hackspett
-Nötkråka
-Ullticka
-Grön sköldmossa
-Hasselsopp
-Stubbspretmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
         <v/>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         <v>45566</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46174</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>45517</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45368</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44539</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11637-2025</t>
+          <t>A 11278-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2081,14 +2081,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45727</v>
+        <v>46080</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2100,28 +2100,23 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2142,711 +2137,716 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 35099-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 15523-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Thymalus limbatus
+Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 37012-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44806</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 11637-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 35099-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45852</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 11278-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46080</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 15523-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Thymalus limbatus
-Vanlig flatbagge</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 27240-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 37012-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44806</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>10</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
         <v/>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>46052</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45042</v>
+        <v>45393</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3241,46 +3241,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45447</v>
+        <v>45127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3343,46 +3343,42 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
@@ -3406,7 +3402,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3512,7 @@
         <v>46090</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3609,7 +3605,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3623,10 +3619,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45559</v>
+        <v>45305</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,16 +3635,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3663,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3675,46 +3671,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 44857-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45362</v>
+        <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,17 +3744,17 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3780,50 +3780,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3837,10 +3833,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45393</v>
+        <v>45559</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3853,17 +3849,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3877,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3893,42 +3889,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44857-2025</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3942,10 +3938,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45918</v>
+        <v>45042</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3958,16 +3954,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3982,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3994,46 +3990,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4047,10 +4043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45127</v>
+        <v>45447</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4063,7 +4059,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4096,49 +4092,53 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 290-2025</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45656</v>
+        <v>45362</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4208,42 +4208,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 290-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4257,10 +4261,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45305</v>
+        <v>45656</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4273,13 +4277,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4313,39 +4317,35 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
         <v/>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46052</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44601</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44656</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23751-2022</t>
+          <t>A 64156-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44722</v>
+        <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4815,8 +4815,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4859,7 +4864,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64156-2021</t>
+          <t>A 23751-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4869,14 +4874,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44510</v>
+        <v>44722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4888,13 +4893,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>44519</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44830</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44734</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44609</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>44632</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44488</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>44748</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44843</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44609</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44589</v>
+        <v>45483</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6120,7 +6120,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44824</v>
+        <v>44839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44916</v>
+        <v>45553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6222,8 +6222,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6266,7 +6271,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11676-2024</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6280,10 +6285,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45373</v>
+        <v>45093</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6296,7 +6301,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6339,7 +6344,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6353,10 +6358,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44479</v>
+        <v>45056</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6369,7 +6374,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6412,7 +6417,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 11676-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6426,10 +6431,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44937</v>
+        <v>45373</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6442,7 +6447,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6485,7 +6490,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6495,14 +6500,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44796</v>
+        <v>45250</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6515,7 +6520,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6558,7 +6563,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6572,10 +6577,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45093</v>
+        <v>45397</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6588,7 +6593,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6631,7 +6636,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6645,10 +6650,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45231</v>
+        <v>45263</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6661,7 +6666,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6704,7 +6709,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6714,14 +6719,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45540</v>
+        <v>45334</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6734,7 +6739,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6777,7 +6782,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6791,10 +6796,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45553</v>
+        <v>45043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6806,13 +6811,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45438</v>
+        <v>44484</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6928,7 +6928,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45001</v>
+        <v>45134</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45134</v>
+        <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7074,7 +7074,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7088,10 +7088,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45309</v>
+        <v>45670</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7103,8 +7103,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>3.8</v>
+        <v>18.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7147,7 +7152,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7161,10 +7166,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45163</v>
+        <v>45666</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7177,7 +7182,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7220,7 +7225,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7234,10 +7239,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45421</v>
+        <v>45231</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7250,7 +7255,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>5.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7293,7 +7298,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7307,10 +7312,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46031</v>
+        <v>45554</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7323,7 +7328,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7366,7 +7371,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26863-2025</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7380,10 +7385,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45810</v>
+        <v>45047</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7396,7 +7401,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7439,7 +7444,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7453,10 +7458,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45730</v>
+        <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7468,13 +7473,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7517,7 +7517,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7527,14 +7527,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45241</v>
+        <v>45068</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45911</v>
+        <v>46090</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7619,8 +7619,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7663,7 +7668,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 12547-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7677,10 +7682,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45539</v>
+        <v>46090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7692,8 +7697,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7736,7 +7746,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7750,10 +7760,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44965</v>
+        <v>45740</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7766,7 +7776,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7809,7 +7819,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7823,10 +7833,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45047</v>
+        <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7838,8 +7848,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7882,7 +7897,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7892,14 +7907,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45047</v>
+        <v>45112</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7911,8 +7926,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7955,7 +7975,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 11794-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7965,14 +7985,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44986</v>
+        <v>44994</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7985,7 +8005,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>12.8</v>
+        <v>7.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8028,7 +8048,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8042,10 +8062,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45091</v>
+        <v>44950</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8058,7 +8078,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8101,7 +8121,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8115,10 +8135,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45740</v>
+        <v>46101</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8131,7 +8151,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8174,7 +8194,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 51659-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8188,10 +8208,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45337</v>
+        <v>44462</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8204,7 +8224,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8247,7 +8267,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8261,10 +8281,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46055</v>
+        <v>45236</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8277,7 +8297,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8320,7 +8340,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8334,10 +8354,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45672</v>
+        <v>45001</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8350,7 +8370,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8393,7 +8413,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8407,10 +8427,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45068</v>
+        <v>45113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8423,7 +8443,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8466,7 +8486,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8480,10 +8500,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45068</v>
+        <v>44993</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8496,7 +8516,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8539,7 +8559,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8553,10 +8573,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45973</v>
+        <v>44916</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8568,13 +8588,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8617,7 +8632,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8631,10 +8646,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45670</v>
+        <v>45553</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8648,11 +8663,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>18.8</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8695,7 +8710,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8705,14 +8720,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44839</v>
+        <v>45204</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8725,7 +8740,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8768,7 +8783,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11794-2023</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8782,10 +8797,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44994</v>
+        <v>46126</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8798,7 +8813,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8841,7 +8856,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8855,10 +8870,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46073</v>
+        <v>45163</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8871,7 +8886,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8914,7 +8929,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8928,10 +8943,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45098</v>
+        <v>45840</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8944,7 +8959,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8987,7 +9002,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9001,10 +9016,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45128</v>
+        <v>45911</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9017,7 +9032,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9060,7 +9075,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9074,10 +9089,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45128</v>
+        <v>44796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9090,7 +9105,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9133,7 +9148,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9143,14 +9158,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45250</v>
+        <v>45085</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9163,7 +9178,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9206,7 +9221,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9220,10 +9235,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45270</v>
+        <v>44824</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9236,7 +9251,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9279,7 +9294,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9293,10 +9308,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44484</v>
+        <v>44748</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9309,7 +9324,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9352,7 +9367,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9366,10 +9381,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46090</v>
+        <v>45127</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9381,13 +9396,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9430,7 +9440,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51659-2021</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9444,10 +9454,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44462</v>
+        <v>45270</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9460,7 +9470,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9503,7 +9513,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9517,10 +9527,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>45539</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9533,7 +9543,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9576,7 +9586,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9590,10 +9600,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46002</v>
+        <v>44479</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9606,7 +9616,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.9</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9649,7 +9659,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 12547-2026</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9663,10 +9673,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46090</v>
+        <v>45553</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9684,7 +9694,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9727,7 +9737,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9741,10 +9751,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45560</v>
+        <v>45740</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9757,7 +9767,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9800,7 +9810,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9814,10 +9824,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45342</v>
+        <v>46155</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9829,8 +9839,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9873,7 +9888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9887,10 +9902,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46009</v>
+        <v>45128</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9902,13 +9917,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9951,7 +9961,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9965,10 +9975,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46009</v>
+        <v>45128</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9980,13 +9990,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10029,7 +10034,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10043,10 +10048,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46009</v>
+        <v>45769</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10058,13 +10063,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45559</v>
+        <v>45098</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10180,7 +10180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44998</v>
+        <v>46167</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10253,7 +10253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46101</v>
+        <v>45153</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10282,8 +10282,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10326,7 +10331,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10336,14 +10341,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45068</v>
+        <v>45813</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10356,7 +10361,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10399,7 +10404,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10413,10 +10418,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45174</v>
+        <v>46174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10428,13 +10433,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44848</v>
+        <v>46174</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10550,7 +10550,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45236</v>
+        <v>44589</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10623,7 +10623,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10633,14 +10633,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44989</v>
+        <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10696,7 +10696,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10706,14 +10706,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44989</v>
+        <v>44965</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10769,7 +10769,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10783,10 +10783,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46126</v>
+        <v>45342</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10842,7 +10842,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10856,10 +10856,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44950</v>
+        <v>45047</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45001</v>
+        <v>46182</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10988,7 +10988,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11002,10 +11002,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45397</v>
+        <v>46189</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11015,6 +11015,11 @@
       <c r="G125" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -11061,7 +11066,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11075,10 +11080,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45840</v>
+        <v>46189</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11090,8 +11095,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11134,7 +11144,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11148,10 +11158,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44764</v>
+        <v>46189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11163,8 +11173,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>9.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11207,7 +11222,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11221,10 +11236,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45331</v>
+        <v>46189</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11237,7 +11252,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.8</v>
+        <v>10.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11280,7 +11295,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11294,10 +11309,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45112</v>
+        <v>46189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11311,11 +11326,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11358,7 +11373,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11372,10 +11387,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45014</v>
+        <v>46189</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11387,8 +11402,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>12.1</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11431,7 +11451,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11445,10 +11465,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45263</v>
+        <v>46191</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11460,8 +11480,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11504,7 +11529,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11518,10 +11543,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45421</v>
+        <v>46190</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11533,8 +11558,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11577,7 +11607,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11587,14 +11617,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45204</v>
+        <v>46190</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11606,8 +11636,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11650,7 +11685,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11664,10 +11699,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45769</v>
+        <v>46195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11679,8 +11714,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11723,7 +11763,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11733,14 +11773,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45740</v>
+        <v>44989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11753,7 +11793,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11796,7 +11836,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11806,14 +11846,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46155</v>
+        <v>44989</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11825,13 +11865,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11874,7 +11909,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11888,10 +11923,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45085</v>
+        <v>46197</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11904,7 +11939,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11947,7 +11982,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 47902-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11961,10 +11996,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45056</v>
+        <v>45204</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11977,7 +12012,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12020,7 +12055,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12034,10 +12069,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46167</v>
+        <v>44804</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12050,7 +12085,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12093,7 +12128,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12107,10 +12142,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45127</v>
+        <v>46197</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12123,7 +12158,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12166,7 +12201,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12180,10 +12215,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44993</v>
+        <v>46199</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12195,8 +12230,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12239,7 +12279,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 47902-2023</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12253,10 +12293,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45204</v>
+        <v>45973</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12268,8 +12308,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12312,7 +12357,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12326,10 +12371,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45093</v>
+        <v>46199</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12341,8 +12386,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12385,7 +12435,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12399,10 +12449,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46174</v>
+        <v>46199</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12414,8 +12464,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12458,7 +12513,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12472,10 +12527,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46174</v>
+        <v>44712</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12488,7 +12543,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12531,7 +12586,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12545,10 +12600,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45813</v>
+        <v>45093</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12561,7 +12616,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12604,7 +12659,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12618,10 +12673,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45281</v>
+        <v>46244</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12633,8 +12688,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12677,7 +12737,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12691,10 +12751,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44676</v>
+        <v>44624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12707,7 +12767,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12750,7 +12810,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12764,10 +12824,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44624</v>
+        <v>45069</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12780,7 +12840,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.9</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12823,7 +12883,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12837,10 +12897,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45554</v>
+        <v>46202</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12852,8 +12912,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12896,7 +12961,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12910,10 +12975,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45523</v>
+        <v>44848</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12926,7 +12991,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12969,7 +13034,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12983,10 +13048,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45523</v>
+        <v>44676</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12999,7 +13064,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13042,7 +13107,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13056,10 +13121,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46182</v>
+        <v>45421</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13072,7 +13137,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13115,7 +13180,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13125,14 +13190,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45153</v>
+        <v>46256</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13150,7 +13215,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13193,7 +13258,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13203,14 +13268,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45666</v>
+        <v>46256</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13222,8 +13287,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13266,7 +13336,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13280,10 +13350,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45113</v>
+        <v>46256</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13295,8 +13365,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13339,7 +13414,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13353,10 +13428,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44992</v>
+        <v>46256</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13374,7 +13449,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13417,7 +13492,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13431,10 +13506,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44712</v>
+        <v>45438</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13447,7 +13522,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13490,7 +13565,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13504,10 +13579,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46190</v>
+        <v>46219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13519,13 +13594,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13568,7 +13638,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13582,10 +13652,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13597,13 +13667,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13646,7 +13711,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13660,10 +13725,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46189</v>
+        <v>45730</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13677,11 +13742,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13724,7 +13789,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13738,10 +13803,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46190</v>
+        <v>44764</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13753,13 +13818,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13802,7 +13862,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13816,10 +13876,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46189</v>
+        <v>46002</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13831,13 +13891,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13880,7 +13935,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13894,10 +13949,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13909,13 +13964,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13958,7 +14008,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13972,10 +14022,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46189</v>
+        <v>45337</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13988,7 +14038,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>10.7</v>
+        <v>4.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14031,7 +14081,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14045,10 +14095,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46189</v>
+        <v>45421</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14060,13 +14110,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14109,7 +14154,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14123,10 +14168,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46191</v>
+        <v>46222</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14138,13 +14183,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14187,7 +14227,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14201,10 +14241,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45616</v>
+        <v>46002</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14217,7 +14257,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14260,7 +14300,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14274,10 +14314,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46195</v>
+        <v>46009</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14291,11 +14331,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14338,7 +14378,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14352,10 +14392,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45553</v>
+        <v>45559</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14367,13 +14407,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14416,7 +14451,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14430,10 +14465,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45043</v>
+        <v>46009</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14445,8 +14480,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14489,7 +14529,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14503,10 +14543,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45483</v>
+        <v>46273</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14518,8 +14558,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14562,7 +14607,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14576,10 +14621,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44988</v>
+        <v>46273</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14597,7 +14642,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14640,7 +14685,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14654,10 +14699,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44804</v>
+        <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14669,8 +14714,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14713,7 +14763,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14727,10 +14777,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46197</v>
+        <v>46273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14742,8 +14792,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14786,7 +14841,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14800,10 +14855,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46197</v>
+        <v>46273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14815,8 +14870,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14859,7 +14919,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14873,10 +14933,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14894,7 +14954,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14937,7 +14997,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14951,10 +15011,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46199</v>
+        <v>46274</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14966,13 +15026,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15015,7 +15070,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15029,10 +15084,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46199</v>
+        <v>45540</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15044,13 +15099,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15093,7 +15143,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15107,10 +15157,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15122,13 +15172,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15171,7 +15216,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15185,10 +15230,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46202</v>
+        <v>46009</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15202,11 +15247,11 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15249,7 +15294,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15263,10 +15308,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45069</v>
+        <v>46273</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15278,8 +15323,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15322,7 +15372,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15336,10 +15386,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45163</v>
+        <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15351,8 +15401,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15395,7 +15450,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15409,10 +15464,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45762</v>
+        <v>46230</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15480,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15523,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15482,10 +15537,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45056</v>
+        <v>46273</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15497,8 +15552,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15541,7 +15601,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15555,10 +15615,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15576,7 +15636,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15619,7 +15679,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15633,10 +15693,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15654,7 +15714,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15697,7 +15757,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15711,10 +15771,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45646</v>
+        <v>45523</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15727,7 +15787,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15770,7 +15830,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15780,14 +15840,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45334</v>
+        <v>45523</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15800,7 +15860,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15843,7 +15903,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 36996-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15857,10 +15917,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15878,7 +15938,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15921,7 +15981,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 36997-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15935,10 +15995,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15956,7 +16016,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15999,7 +16059,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16013,10 +16073,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44950</v>
+        <v>46273</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16028,8 +16088,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16072,7 +16137,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16082,14 +16147,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46256</v>
+        <v>45331</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16101,13 +16166,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16150,7 +16210,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16160,14 +16220,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46256</v>
+        <v>44998</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16179,13 +16239,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16228,7 +16283,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 38008-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16242,10 +16297,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46219</v>
+        <v>46280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16257,8 +16312,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16301,7 +16361,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16315,10 +16375,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46219</v>
+        <v>44950</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16331,7 +16391,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16374,7 +16434,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 38021-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16388,10 +16448,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45601</v>
+        <v>46280</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16403,8 +16463,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16447,7 +16512,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16461,10 +16526,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46219</v>
+        <v>44992</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16476,8 +16541,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16520,7 +16590,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16534,10 +16604,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46222</v>
+        <v>45056</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16550,7 +16620,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16593,7 +16663,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16607,10 +16677,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44589</v>
+        <v>46031</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16623,7 +16693,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.7</v>
+        <v>12</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16666,7 +16736,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16680,10 +16750,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44748</v>
+        <v>44937</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16696,7 +16766,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16739,7 +16809,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16749,14 +16819,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45112</v>
+        <v>45281</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16768,13 +16838,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16817,7 +16882,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16831,10 +16896,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46273</v>
+        <v>45560</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16846,13 +16911,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16895,7 +16955,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16909,10 +16969,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46273</v>
+        <v>45091</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16924,13 +16984,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16973,7 +17028,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16987,10 +17042,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46273</v>
+        <v>45001</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17002,13 +17057,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17051,7 +17101,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17065,10 +17115,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45553</v>
+        <v>46055</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17080,13 +17130,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17129,7 +17174,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17143,10 +17188,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46273</v>
+        <v>44988</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17164,7 +17209,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17207,7 +17252,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17221,10 +17266,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46273</v>
+        <v>45309</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17236,13 +17281,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17285,7 +17325,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17299,10 +17339,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46273</v>
+        <v>45762</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17314,13 +17354,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17363,7 +17398,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17377,10 +17412,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17398,7 +17433,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17441,7 +17476,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17455,10 +17490,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17476,7 +17511,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17519,7 +17554,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17533,10 +17568,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46230</v>
+        <v>45241</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17549,7 +17584,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17592,7 +17627,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17606,10 +17641,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46273</v>
+        <v>45014</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17621,13 +17656,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>3.1</v>
+        <v>12.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17670,7 +17700,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36996-2026</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17684,10 +17714,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46273</v>
+        <v>45068</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17699,13 +17729,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17748,7 +17773,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 36997-2026</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17762,10 +17787,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46273</v>
+        <v>45068</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17777,13 +17802,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17826,7 +17846,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17840,10 +17860,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46273</v>
+        <v>45616</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17855,13 +17875,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17904,7 +17919,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17914,14 +17929,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46230</v>
+        <v>44986</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17934,7 +17949,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>4.2</v>
+        <v>12.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17977,7 +17992,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17991,10 +18006,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46273</v>
+        <v>45601</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18006,13 +18021,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18055,7 +18065,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18069,10 +18079,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46273</v>
+        <v>45174</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18086,11 +18096,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18133,7 +18143,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18147,10 +18157,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46274</v>
+        <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18163,7 +18173,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18206,7 +18216,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 38021-2026</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18220,10 +18230,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46280</v>
+        <v>45646</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18235,13 +18245,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18301,7 +18306,7 @@
         <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18357,7 +18362,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 38008-2026</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18371,10 +18376,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46280</v>
+        <v>45656</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18386,13 +18391,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18449,10 +18449,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45670</v>
+        <v>45600</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18464,13 +18464,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>9.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18513,7 +18508,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 33334-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18527,10 +18522,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45656</v>
+        <v>45128</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18543,7 +18538,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18586,7 +18581,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18600,10 +18595,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45600</v>
+        <v>45670</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18615,8 +18610,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>2.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18659,7 +18659,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 33334-2023</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18673,10 +18673,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45128</v>
+        <v>45622</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18732,7 +18732,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 10274-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18746,10 +18746,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45622</v>
+        <v>44986</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18805,7 +18805,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 10274-2023</t>
+          <t>A 58548-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18819,10 +18819,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44986</v>
+        <v>45635</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 58548-2024</t>
+          <t>A 26863-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18892,10 +18892,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45635</v>
+        <v>45810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18968,7 +18968,7 @@
         <v>44889</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>44889</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45317</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45762</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>46030</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46256</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46256</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>44459</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 28147-2022</t>
+          <t>A 27395-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44746</v>
+        <v>46189</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -872,23 +872,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -900,18 +905,134 @@
         <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
       <c r="T4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U4" t="n">
+        <v>16</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Entita
+Grantaggsvamp
+Talltita
+Vedticka
+Spillkråka
+Tofsmes
+Smålom</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 28147-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
         <v>15</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>14</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre hackspett
@@ -923,157 +1044,36 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 27395-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16</v>
-      </c>
-      <c r="U5" t="n">
-        <v>16</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Entita
-Grantaggsvamp
-Talltita
-Vedticka
-Spillkråka
-Tofsmes
-Smålom</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
         <v/>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         <v>45566</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46174</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31357-2026</t>
+          <t>A 33104-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1552,20 +1552,20 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1576,21 +1576,133 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Blekspindling agg.
+Jungfrulin
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33104-2024 artfynd.xlsx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33104-2024 karta.png", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33104-2024 georefererad karta.tif", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 33104-2024 karta knärot.png", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33104-2024 FSC-klagomål.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33104-2024 FSC-klagomål mail.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33104-2024 tillsynsbegäran.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33104-2024 tillsynsbegäran mail.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31357-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>11</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>11</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Spillkråka
@@ -1598,148 +1710,36 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 31357-2026 artfynd.xlsx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 31357-2026 karta.png", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 31357-2026 georefererad karta.tif", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 31357-2026 FSC-klagomål.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 31357-2026 FSC-klagomål mail.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 31357-2026 tillsynsbegäran.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 31357-2026 tillsynsbegäran mail.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 31357-2026 prioriterade fågelarter.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 33104-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45517</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Blekspindling agg.
-Jungfrulin
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33104-2024 artfynd.xlsx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33104-2024 karta.png", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33104-2024 georefererad karta.tif", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 33104-2024 karta knärot.png", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33104-2024 FSC-klagomål.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33104-2024 FSC-klagomål mail.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33104-2024 tillsynsbegäran.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33104-2024 tillsynsbegäran mail.docx", "A 33104-2024")</f>
         <v/>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45368</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44539</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11278-2026</t>
+          <t>A 11637-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2081,14 +2081,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46080</v>
+        <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2100,23 +2100,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2137,801 +2142,796 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 11278-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Entita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 15523-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Thymalus limbatus
+Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37012-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44806</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 35099-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>45852</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I21" t="n">
         <v>16.5</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 15523-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S 765-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="I22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Thymalus limbatus
-Vanlig flatbagge</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 27240-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 37012-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44806</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>10</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 11637-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S 765-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Rävticka</t>
-        </is>
-      </c>
       <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/S 765-2025 artfynd.xlsx", "S 765-2025")</f>
         <v/>
@@ -2981,7 +2981,7 @@
         <v>46052</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45393</v>
+        <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3241,46 +3241,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45127</v>
+        <v>45447</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3343,49 +3343,53 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12550-2026</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46090</v>
+        <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3414,13 +3418,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3460,42 +3459,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12557-2026</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3509,10 +3512,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46090</v>
+        <v>45393</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,19 +3527,14 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3570,42 +3568,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 44857-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3619,10 +3617,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45305</v>
+        <v>45918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,17 +3633,17 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3659,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3671,50 +3669,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44857-2025</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3728,10 +3722,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45918</v>
+        <v>45559</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3744,7 +3738,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3784,42 +3778,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3833,10 +3827,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45559</v>
+        <v>45127</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3849,16 +3843,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3873,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3889,42 +3883,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 290-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3938,10 +3932,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45042</v>
+        <v>45656</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3954,13 +3948,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3994,42 +3988,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 12550-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4043,10 +4037,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45447</v>
+        <v>46090</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4058,8 +4052,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4092,53 +4091,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 12557-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4152,10 +4147,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45362</v>
+        <v>46090</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4167,14 +4162,19 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4204,50 +4204,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 290-2025</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4261,10 +4257,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45656</v>
+        <v>45305</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4277,13 +4273,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4317,35 +4313,39 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46052</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44601</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44656</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64156-2021</t>
+          <t>A 23751-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44510</v>
+        <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4815,13 +4815,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4864,7 +4859,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23751-2022</t>
+          <t>A 64156-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4874,14 +4869,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44722</v>
+        <v>44510</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4893,8 +4888,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>44519</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44830</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44734</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44609</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>44632</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44488</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>44748</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44843</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44609</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45483</v>
+        <v>44589</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6120,7 +6120,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44839</v>
+        <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45553</v>
+        <v>44937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6222,13 +6222,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6271,7 +6266,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 11676-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6285,10 +6280,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45093</v>
+        <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6301,7 +6296,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6344,7 +6339,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6358,10 +6353,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45056</v>
+        <v>44479</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6374,7 +6369,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6417,7 +6412,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11676-2024</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6431,10 +6426,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45373</v>
+        <v>44796</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6447,7 +6442,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6490,7 +6485,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6500,14 +6495,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45250</v>
+        <v>45540</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6520,7 +6515,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6563,7 +6558,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6577,10 +6572,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45397</v>
+        <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6593,7 +6588,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6636,7 +6631,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6650,10 +6645,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45263</v>
+        <v>45438</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6666,7 +6661,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6709,7 +6704,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6719,14 +6714,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45334</v>
+        <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6738,8 +6733,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6782,7 +6782,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6796,10 +6796,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45043</v>
+        <v>45231</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44484</v>
+        <v>45093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6928,7 +6928,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45134</v>
+        <v>45309</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44589</v>
+        <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7074,7 +7074,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7088,10 +7088,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45670</v>
+        <v>45134</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7103,13 +7103,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>18.8</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7152,7 +7147,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45666</v>
+        <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7182,7 +7177,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7225,7 +7220,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45231</v>
+        <v>45421</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7255,7 +7250,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.7</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7298,7 +7293,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7312,10 +7307,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45554</v>
+        <v>45730</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7327,8 +7322,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7371,7 +7371,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45047</v>
+        <v>45241</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7444,7 +7444,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46073</v>
+        <v>45539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7517,7 +7517,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7527,14 +7527,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45068</v>
+        <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46090</v>
+        <v>45047</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7619,13 +7619,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7668,7 +7663,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12547-2026</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7682,10 +7677,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46090</v>
+        <v>45047</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7697,13 +7692,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7746,7 +7736,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7756,14 +7746,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45740</v>
+        <v>44986</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7776,7 +7766,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>12.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7819,7 +7809,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7833,10 +7823,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45112</v>
+        <v>45337</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7848,13 +7838,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7897,7 +7882,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7907,14 +7892,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45112</v>
+        <v>45091</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7926,13 +7911,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7975,7 +7955,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11794-2023</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7989,10 +7969,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44994</v>
+        <v>45672</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8005,7 +7985,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8048,7 +8028,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8062,10 +8042,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44950</v>
+        <v>45068</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8078,7 +8058,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8121,7 +8101,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8135,10 +8115,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46101</v>
+        <v>45068</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8151,7 +8131,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8194,7 +8174,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51659-2021</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8208,10 +8188,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44462</v>
+        <v>45670</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8223,8 +8203,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>18.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8267,7 +8252,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8281,10 +8266,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45236</v>
+        <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8297,7 +8282,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8340,7 +8325,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 11794-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8354,10 +8339,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45001</v>
+        <v>44994</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8370,7 +8355,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8413,7 +8398,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8427,10 +8412,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45113</v>
+        <v>45740</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8443,7 +8428,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8486,7 +8471,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8500,10 +8485,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44993</v>
+        <v>45098</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8516,7 +8501,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8559,7 +8544,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8573,10 +8558,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44916</v>
+        <v>45128</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8589,7 +8574,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8632,7 +8617,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8646,10 +8631,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45553</v>
+        <v>45128</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8661,13 +8646,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8710,7 +8690,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8724,10 +8704,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45204</v>
+        <v>45250</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8740,7 +8720,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8783,7 +8763,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8797,10 +8777,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46126</v>
+        <v>45270</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8813,7 +8793,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8856,7 +8836,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8870,10 +8850,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45163</v>
+        <v>44484</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8886,7 +8866,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8929,7 +8909,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 51659-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8943,10 +8923,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45840</v>
+        <v>44462</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8959,7 +8939,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9002,7 +8982,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9016,10 +8996,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45911</v>
+        <v>45560</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9032,7 +9012,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9075,7 +9055,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9089,10 +9069,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44796</v>
+        <v>45342</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9105,7 +9085,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9148,7 +9128,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9162,10 +9142,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45085</v>
+        <v>45911</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9178,7 +9158,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9221,7 +9201,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9235,10 +9215,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44824</v>
+        <v>44998</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9251,7 +9231,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9294,7 +9274,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9304,14 +9284,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44748</v>
+        <v>45068</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9324,7 +9304,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9367,7 +9347,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9381,10 +9361,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45127</v>
+        <v>45174</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9396,8 +9376,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9440,7 +9425,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9454,10 +9439,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45270</v>
+        <v>44848</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9470,7 +9455,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9513,7 +9498,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9527,10 +9512,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45539</v>
+        <v>45236</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9543,7 +9528,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9586,7 +9571,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9596,14 +9581,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44479</v>
+        <v>44989</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9616,7 +9601,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9659,7 +9644,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9669,14 +9654,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45553</v>
+        <v>44989</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9688,13 +9673,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9737,7 +9717,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9751,10 +9731,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45740</v>
+        <v>44950</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9767,7 +9747,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9810,7 +9790,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9824,10 +9804,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46155</v>
+        <v>45001</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9839,13 +9819,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9888,7 +9863,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9902,10 +9877,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45128</v>
+        <v>45397</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9918,7 +9893,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9961,7 +9936,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9975,10 +9950,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45128</v>
+        <v>44764</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9991,7 +9966,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10034,7 +10009,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10048,10 +10023,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45769</v>
+        <v>45973</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10063,8 +10038,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10107,7 +10087,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10121,10 +10101,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45098</v>
+        <v>45769</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10137,7 +10117,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10180,7 +10160,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10194,10 +10174,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10209,8 +10189,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10253,7 +10238,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10267,10 +10252,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45153</v>
+        <v>45331</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10282,13 +10267,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10331,7 +10311,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10345,10 +10325,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45813</v>
+        <v>46167</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10361,7 +10341,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10404,7 +10384,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10418,10 +10398,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46174</v>
+        <v>45112</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10433,8 +10413,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10477,7 +10462,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10491,10 +10476,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46174</v>
+        <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10507,7 +10492,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10550,7 +10535,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10564,10 +10549,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44589</v>
+        <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10580,7 +10565,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10623,7 +10608,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10637,10 +10622,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45163</v>
+        <v>45014</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10653,7 +10638,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>12.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10696,7 +10681,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10710,10 +10695,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44965</v>
+        <v>46009</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10725,8 +10710,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10769,7 +10759,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10783,10 +10773,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45342</v>
+        <v>46009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10798,8 +10788,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10842,7 +10837,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10856,10 +10851,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45047</v>
+        <v>45263</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10872,7 +10867,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10915,7 +10910,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10929,10 +10924,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46182</v>
+        <v>45421</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10945,7 +10940,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10988,7 +10983,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11002,10 +10997,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46189</v>
+        <v>46009</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11019,11 +11014,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11066,7 +11061,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11080,10 +11075,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46189</v>
+        <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11095,13 +11090,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11144,7 +11134,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11154,14 +11144,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46189</v>
+        <v>45204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11173,13 +11163,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11222,7 +11207,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11236,10 +11221,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46189</v>
+        <v>45740</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11252,7 +11237,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>10.7</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11295,7 +11280,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11309,10 +11294,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46189</v>
+        <v>45085</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11324,13 +11309,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11373,7 +11353,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11387,10 +11367,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46189</v>
+        <v>46031</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11402,13 +11382,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11451,7 +11426,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11465,10 +11440,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46191</v>
+        <v>45056</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11480,13 +11455,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11529,7 +11499,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11543,10 +11513,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46190</v>
+        <v>46174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11558,13 +11528,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11607,7 +11572,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11621,10 +11586,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46190</v>
+        <v>46174</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11636,13 +11601,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11685,7 +11645,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11699,10 +11659,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46195</v>
+        <v>45813</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11714,13 +11674,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11763,7 +11718,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11773,14 +11728,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44989</v>
+        <v>45127</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11793,7 +11748,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11836,7 +11791,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11846,14 +11801,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44989</v>
+        <v>44993</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11866,7 +11821,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11909,7 +11864,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11923,10 +11878,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46197</v>
+        <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11939,7 +11894,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11999,7 +11954,7 @@
         <v>45204</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12055,7 +12010,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12069,10 +12024,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44804</v>
+        <v>45093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12085,7 +12040,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12128,7 +12083,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12142,10 +12097,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46197</v>
+        <v>45281</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12158,7 +12113,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12201,7 +12156,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12215,10 +12170,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46199</v>
+        <v>44676</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12230,13 +12185,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12279,7 +12229,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12293,10 +12243,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45973</v>
+        <v>44624</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12308,13 +12258,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>7.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12357,7 +12302,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12371,10 +12316,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46199</v>
+        <v>46073</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12386,13 +12331,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12435,7 +12375,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12449,10 +12389,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46199</v>
+        <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12464,13 +12404,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12513,7 +12448,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12527,10 +12462,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44712</v>
+        <v>45554</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12543,7 +12478,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12586,7 +12521,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12600,10 +12535,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45093</v>
+        <v>45523</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12616,7 +12551,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12659,7 +12594,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12673,10 +12608,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46244</v>
+        <v>45523</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12688,13 +12623,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12737,7 +12667,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12751,10 +12681,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44624</v>
+        <v>45153</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12766,8 +12696,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12810,7 +12745,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12824,10 +12759,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45069</v>
+        <v>45666</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12840,7 +12775,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12883,7 +12818,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12897,10 +12832,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46202</v>
+        <v>45113</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12912,13 +12847,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12961,7 +12891,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12975,10 +12905,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44848</v>
+        <v>46090</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12990,8 +12920,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13034,7 +12969,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13048,10 +12983,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44676</v>
+        <v>44992</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13063,8 +12998,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13107,7 +13047,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 12547-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13121,10 +13061,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45421</v>
+        <v>46090</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13136,8 +13076,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13180,7 +13125,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13190,14 +13135,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46256</v>
+        <v>44712</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13209,13 +13154,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13258,7 +13198,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13268,14 +13208,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46256</v>
+        <v>46190</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13293,7 +13233,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13336,7 +13276,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13350,10 +13290,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46256</v>
+        <v>46189</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13371,7 +13311,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13414,7 +13354,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13428,10 +13368,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46256</v>
+        <v>46189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13449,7 +13389,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13492,7 +13432,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13506,10 +13446,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45438</v>
+        <v>46190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13521,8 +13461,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13565,7 +13510,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13579,10 +13524,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46219</v>
+        <v>46189</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13594,8 +13539,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13638,7 +13588,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13652,10 +13602,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46219</v>
+        <v>46189</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13667,8 +13617,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13711,7 +13666,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13725,10 +13680,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45730</v>
+        <v>46189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13740,13 +13695,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>4.8</v>
+        <v>10.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13789,7 +13739,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13803,10 +13753,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44764</v>
+        <v>46189</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13818,8 +13768,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13862,7 +13817,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13876,10 +13831,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46002</v>
+        <v>46191</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13891,8 +13846,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13935,7 +13895,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13949,10 +13909,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46219</v>
+        <v>46101</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13965,7 +13925,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14008,7 +13968,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14022,10 +13982,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45337</v>
+        <v>46195</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14037,8 +13997,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14081,7 +14046,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14095,10 +14060,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45421</v>
+        <v>45616</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14111,7 +14076,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14154,7 +14119,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14168,10 +14133,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46222</v>
+        <v>45553</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14183,8 +14148,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14227,7 +14197,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14241,10 +14211,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46002</v>
+        <v>45043</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14257,7 +14227,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14300,7 +14270,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14314,10 +14284,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46009</v>
+        <v>45483</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14329,13 +14299,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14378,7 +14343,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14392,10 +14357,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45559</v>
+        <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14408,7 +14373,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14451,7 +14416,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14465,10 +14430,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46009</v>
+        <v>46197</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14480,13 +14445,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14529,7 +14489,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14543,10 +14503,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46273</v>
+        <v>44988</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14564,7 +14524,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14607,7 +14567,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14621,10 +14581,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46273</v>
+        <v>44804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14636,13 +14596,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14685,7 +14640,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14699,10 +14654,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46273</v>
+        <v>46199</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14720,7 +14675,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14763,7 +14718,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14777,10 +14732,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46273</v>
+        <v>46199</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14798,7 +14753,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14841,7 +14796,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14855,10 +14810,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46273</v>
+        <v>46199</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14876,7 +14831,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14919,7 +14874,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14933,10 +14888,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46273</v>
+        <v>45069</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14948,13 +14903,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14997,7 +14947,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15011,10 +14961,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46274</v>
+        <v>45163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15027,7 +14977,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15070,7 +15020,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15084,10 +15034,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45540</v>
+        <v>46244</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15099,8 +15049,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15143,7 +15098,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15157,10 +15112,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46230</v>
+        <v>46126</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15173,7 +15128,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15216,7 +15171,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15230,10 +15185,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46009</v>
+        <v>45762</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15245,13 +15200,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15294,7 +15244,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15308,10 +15258,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46273</v>
+        <v>46202</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15329,7 +15279,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15372,7 +15322,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15386,10 +15336,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46273</v>
+        <v>45056</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15401,13 +15351,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15450,7 +15395,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15464,10 +15409,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46230</v>
+        <v>45553</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15479,8 +15424,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15523,7 +15473,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15537,10 +15487,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15601,7 +15551,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15615,10 +15565,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46273</v>
+        <v>45646</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15630,13 +15580,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15679,7 +15624,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15689,14 +15634,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46273</v>
+        <v>45334</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15708,13 +15653,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15757,7 +15697,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15771,10 +15711,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45523</v>
+        <v>45840</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15787,7 +15727,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15830,7 +15770,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15844,10 +15784,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45523</v>
+        <v>44950</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15860,7 +15800,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15903,7 +15843,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36996-2026</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15917,10 +15857,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46273</v>
+        <v>45601</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15932,13 +15872,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15981,7 +15916,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36997-2026</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15995,10 +15930,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46273</v>
+        <v>44589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16010,13 +15945,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16059,7 +15989,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16073,10 +16003,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46273</v>
+        <v>44748</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16088,13 +16018,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16137,7 +16062,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16151,10 +16076,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45331</v>
+        <v>46256</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16166,8 +16091,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16210,7 +16140,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16224,10 +16154,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44998</v>
+        <v>46256</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16239,8 +16169,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16283,7 +16218,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 38008-2026</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16293,14 +16228,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46280</v>
+        <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16318,7 +16253,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16361,7 +16296,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16371,14 +16306,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44950</v>
+        <v>46256</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16390,8 +16325,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16434,7 +16374,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38021-2026</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16444,14 +16384,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46280</v>
+        <v>46256</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16469,7 +16409,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16512,7 +16452,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16526,10 +16466,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44992</v>
+        <v>45553</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16547,7 +16487,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16590,7 +16530,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16604,10 +16544,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45056</v>
+        <v>46219</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16620,7 +16560,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16663,7 +16603,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16677,10 +16617,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46031</v>
+        <v>46219</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16693,7 +16633,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16736,7 +16676,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16750,10 +16690,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44937</v>
+        <v>46219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16766,7 +16706,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16809,7 +16749,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16823,10 +16763,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45281</v>
+        <v>46222</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16839,7 +16779,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16882,7 +16822,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16896,10 +16836,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45560</v>
+        <v>46273</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16911,8 +16851,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16955,7 +16900,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16969,10 +16914,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45091</v>
+        <v>46273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16984,8 +16929,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17028,7 +16978,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17042,10 +16992,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45001</v>
+        <v>46273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17057,8 +17007,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17101,7 +17056,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17115,10 +17070,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46055</v>
+        <v>46273</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17130,8 +17085,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17174,7 +17134,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17188,10 +17148,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44988</v>
+        <v>46273</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17209,7 +17169,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17252,7 +17212,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17266,10 +17226,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45309</v>
+        <v>46273</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17281,8 +17241,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17325,7 +17290,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17339,10 +17304,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45762</v>
+        <v>46273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17354,8 +17319,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17398,7 +17368,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17412,10 +17382,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17433,7 +17403,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17476,7 +17446,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17490,10 +17460,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45553</v>
+        <v>46230</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17505,13 +17475,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17554,7 +17519,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17568,10 +17533,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45241</v>
+        <v>46273</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17583,8 +17548,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17627,7 +17597,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 36996-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17641,10 +17611,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45014</v>
+        <v>46273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17656,8 +17626,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>12.1</v>
+        <v>0.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17700,7 +17675,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 36997-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17714,10 +17689,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45068</v>
+        <v>46273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17729,8 +17704,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17773,7 +17753,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17787,10 +17767,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45068</v>
+        <v>46273</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17802,8 +17782,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17846,7 +17831,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17860,10 +17845,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45616</v>
+        <v>46230</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17876,7 +17861,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17919,7 +17904,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17929,14 +17914,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44986</v>
+        <v>46273</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17948,8 +17933,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>12.8</v>
+        <v>0.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17992,7 +17982,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18006,10 +17996,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45601</v>
+        <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18021,8 +18011,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18065,7 +18060,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 61470-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18079,10 +18074,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45174</v>
+        <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18094,13 +18089,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18143,7 +18133,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18157,10 +18147,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45672</v>
+        <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18173,7 +18163,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18216,7 +18206,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18230,10 +18220,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45646</v>
+        <v>45670</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18245,8 +18235,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18289,7 +18284,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61470-2024</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18303,10 +18298,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45646</v>
+        <v>45656</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18319,7 +18314,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18362,7 +18357,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18376,10 +18371,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45656</v>
+        <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18392,7 +18387,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18435,7 +18430,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 38021-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18449,10 +18444,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45600</v>
+        <v>46280</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18464,8 +18459,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18525,7 +18525,7 @@
         <v>45128</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18595,10 +18595,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45670</v>
+        <v>45622</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18610,13 +18610,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18659,7 +18654,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 38008-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18673,10 +18668,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45622</v>
+        <v>46280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18688,8 +18683,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18749,7 +18749,7 @@
         <v>44986</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45635</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>44889</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>44889</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45317</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45762</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>46030</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46256</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46256</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>44459</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>46189</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>44746</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45566</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46059</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46174</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>44589</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>45985</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45368</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>44539</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>46080</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>46106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44806</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45852</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>46052</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45042</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45447</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45393</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45559</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45127</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45656</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46090</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46090</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45305</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46052</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44601</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44656</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>44510</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44519</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44830</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44734</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44609</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44830</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>44632</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44488</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>44748</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>44593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44843</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44609</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44589</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44479</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44796</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45540</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>45438</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45231</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45309</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45134</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45421</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45730</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45241</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>45047</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>45047</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44986</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>45337</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45091</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45672</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>45068</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45068</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45670</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44994</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45740</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45098</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45128</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45128</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45250</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45270</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44484</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44462</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45560</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45342</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45911</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44998</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45068</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45174</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44848</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45236</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44989</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44989</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44950</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45001</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45397</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44764</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45973</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45769</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46155</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45331</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>46167</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45112</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45014</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>46009</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>46009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45263</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45421</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>46009</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45740</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>45085</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>46031</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45056</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>46174</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>46174</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45813</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45127</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44993</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>45204</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45281</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>44676</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44624</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>46073</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45554</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45523</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45523</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45153</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45666</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45113</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>46090</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44992</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>46090</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44712</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>46190</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46189</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>46189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>46190</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>46189</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46189</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>46189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>46189</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>46191</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>46101</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>46195</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45616</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>45553</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45043</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45483</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>46197</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44988</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>46199</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>46199</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>46199</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45069</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>46244</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>46126</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45762</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>46202</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45056</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45553</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45553</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45646</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45334</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45840</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44950</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45601</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44748</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>46256</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>46256</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>46256</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>46256</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45553</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>46219</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>46219</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>46219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>46222</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>46273</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>46273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>46273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>46273</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>46273</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>46273</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>46273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46273</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>46230</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>46273</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>46273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>46273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>46273</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>46230</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>46273</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>46274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45670</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45656</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>46280</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45128</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>45622</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>46280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44986</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45635</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>44889</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>44889</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45317</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45762</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>46030</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46256</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46256</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE237"/>
+  <dimension ref="A1:AE236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 27395-2026</t>
+          <t>A 28147-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46189</v>
+        <v>44746</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -749,28 +749,23 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -782,18 +777,139 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
       </c>
       <c r="T3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre hackspett
+Nötkråka
+Ullticka
+Grön sköldmossa
+Hasselsopp
+Stubbspretmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 27395-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
         <v>16</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>16</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Entita
@@ -805,152 +921,36 @@
 Smålom</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 28147-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre hackspett
-Nötkråka
-Ullticka
-Grön sköldmossa
-Hasselsopp
-Stubbspretmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
         <v/>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24919-2026</t>
+          <t>A 33104-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46174</v>
+        <v>45517</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1233,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1245,9 +1245,121 @@
         <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Blekspindling agg.
+Jungfrulin
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33104-2024 artfynd.xlsx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33104-2024 karta.png", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33104-2024 georefererad karta.tif", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 33104-2024 karta knärot.png", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33104-2024 FSC-klagomål.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33104-2024 FSC-klagomål mail.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33104-2024 tillsynsbegäran.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33104-2024 tillsynsbegäran mail.docx", "A 33104-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 24919-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Svinrot
@@ -1255,107 +1367,107 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 24919-2026 artfynd.xlsx", "A 24919-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 24919-2026 karta.png", "A 24919-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 24919-2026 georefererad karta.tif", "A 24919-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 24919-2026 FSC-klagomål.docx", "A 24919-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 24919-2026 FSC-klagomål mail.docx", "A 24919-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 24919-2026 tillsynsbegäran.docx", "A 24919-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 24919-2026 tillsynsbegäran mail.docx", "A 24919-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 4468-2022</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>44589</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>4.8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>12</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>12</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Spillkråka
@@ -1363,111 +1475,111 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 4468-2022 artfynd.xlsx", "A 4468-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 4468-2022 karta.png", "A 4468-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 4468-2022 georefererad karta.tif", "A 4468-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 4468-2022 FSC-klagomål.docx", "A 4468-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 4468-2022 FSC-klagomål mail.docx", "A 4468-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 4468-2022 tillsynsbegäran.docx", "A 4468-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 4468-2022 tillsynsbegäran mail.docx", "A 4468-2022")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 4468-2022 prioriterade fågelarter.docx", "A 4468-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 31357-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>2.5</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>11</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>11</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Spillkråka
@@ -1475,148 +1587,36 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 31357-2026 artfynd.xlsx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 31357-2026 karta.png", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 31357-2026 georefererad karta.tif", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 31357-2026 FSC-klagomål.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 31357-2026 FSC-klagomål mail.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 31357-2026 tillsynsbegäran.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 31357-2026 tillsynsbegäran mail.docx", "A 31357-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 31357-2026 prioriterade fågelarter.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 33104-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45517</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Blekspindling agg.
-Jungfrulin
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33104-2024 artfynd.xlsx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33104-2024 karta.png", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33104-2024 georefererad karta.tif", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 33104-2024 karta knärot.png", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33104-2024 FSC-klagomål.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33104-2024 FSC-klagomål mail.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33104-2024 tillsynsbegäran.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33104-2024 tillsynsbegäran mail.docx", "A 33104-2024")</f>
         <v/>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45368</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44539</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11637-2025</t>
+          <t>A 37012-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45727</v>
+        <v>44806</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1977,28 +1977,23 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2016,714 +2011,719 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 11278-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 35099-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 15523-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Thymalus limbatus
+Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 11637-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 27240-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Skogsödla</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 11278-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46080</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 15523-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Thymalus limbatus
-Vanlig flatbagge</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 37012-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44806</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>10</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 35099-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45852</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
         <v/>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
         <v>45727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>46052</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45042</v>
+        <v>45305</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3122,42 +3122,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3171,10 +3175,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45447</v>
+        <v>45393</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3191,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3220,53 +3224,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44857-2025</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45918</v>
+        <v>45127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,16 +3296,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3336,42 +3336,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45362</v>
+        <v>45559</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3401,17 +3401,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3437,50 +3437,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 12550-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3494,10 +3490,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45559</v>
+        <v>46090</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3509,17 +3505,22 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3534,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3546,46 +3547,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 12557-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3599,10 +3600,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45393</v>
+        <v>46090</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3614,14 +3615,19 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3655,42 +3661,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12550-2026</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3704,10 +3710,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46090</v>
+        <v>45042</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3719,13 +3725,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3769,38 +3770,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12557-2026</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3814,10 +3815,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>45447</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,19 +3830,14 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3868,49 +3864,53 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45127</v>
+        <v>45362</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3976,39 +3976,43 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
@@ -4032,7 +4036,7 @@
         <v>45656</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4120,7 +4124,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 44857-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4134,10 +4138,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45305</v>
+        <v>45918</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4150,17 +4154,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4174,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4186,43 +4190,39 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44601</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44656</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44519</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44508</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44734</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44609</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44830</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44632</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44488</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44748</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5043-2022</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44593</v>
+        <v>44796</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5627,7 +5627,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45105-2022</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44843</v>
+        <v>45600</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5700,7 +5700,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8050-2022</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44609</v>
+        <v>45085</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 67508-2021</t>
+          <t>A 5043-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44524</v>
+        <v>44593</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41979-2022</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44830</v>
+        <v>44824</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5875,13 +5875,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5924,7 +5919,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 67508-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5938,10 +5933,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44824</v>
+        <v>44524</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5954,7 +5949,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5997,7 +5992,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 41979-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6011,10 +6006,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44589</v>
+        <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6024,6 +6019,11 @@
       <c r="G58" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -6070,7 +6070,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11676-2024</t>
+          <t>A 45105-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45373</v>
+        <v>44843</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 33334-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44916</v>
+        <v>45128</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44479</v>
+        <v>45483</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44937</v>
+        <v>44748</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 8050-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45093</v>
+        <v>44609</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44796</v>
+        <v>45670</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6464,8 +6464,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6508,7 +6513,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6522,10 +6527,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45540</v>
+        <v>45127</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6538,7 +6543,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6581,7 +6586,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6595,10 +6600,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45438</v>
+        <v>44839</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6611,7 +6616,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6654,7 +6659,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6668,10 +6673,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45553</v>
+        <v>45270</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6683,13 +6688,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45231</v>
+        <v>45539</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6805,7 +6805,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45001</v>
+        <v>45622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45309</v>
+        <v>45553</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6907,8 +6907,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6951,7 +6956,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6965,10 +6970,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45134</v>
+        <v>45093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6981,7 +6986,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7024,7 +7029,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 10274-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7038,10 +7043,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45163</v>
+        <v>44986</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7054,7 +7059,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7097,7 +7102,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7111,10 +7116,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45421</v>
+        <v>44479</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7127,7 +7132,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7170,7 +7175,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7184,10 +7189,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45730</v>
+        <v>45553</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7201,11 +7206,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7248,7 +7253,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 11676-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7262,10 +7267,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45241</v>
+        <v>45373</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7278,7 +7283,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7321,7 +7326,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 58548-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7335,10 +7340,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45539</v>
+        <v>45635</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7351,7 +7356,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7394,7 +7399,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7408,10 +7413,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44965</v>
+        <v>45056</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7424,7 +7429,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7467,7 +7472,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7481,10 +7486,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45047</v>
+        <v>45740</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7497,7 +7502,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7540,7 +7545,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7554,10 +7559,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45047</v>
+        <v>45740</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7570,7 +7575,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7613,7 +7618,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7627,10 +7632,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44986</v>
+        <v>45250</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7643,7 +7648,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>12.8</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7686,7 +7691,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7700,10 +7705,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45091</v>
+        <v>45397</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7716,7 +7721,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7759,7 +7764,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7773,10 +7778,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45337</v>
+        <v>45128</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7789,7 +7794,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7832,7 +7837,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7846,10 +7851,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45672</v>
+        <v>45128</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7862,7 +7867,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7905,7 +7910,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7919,10 +7924,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45840</v>
+        <v>45263</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7935,7 +7940,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7978,7 +7983,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7992,10 +7997,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45068</v>
+        <v>45134</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8008,7 +8013,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8051,7 +8056,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8065,10 +8070,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45068</v>
+        <v>45098</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8081,7 +8086,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8124,7 +8129,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8134,14 +8139,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45740</v>
+        <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8154,7 +8159,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8197,7 +8202,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8211,10 +8216,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45670</v>
+        <v>45911</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8226,13 +8231,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>18.8</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44839</v>
+        <v>45043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11794-2023</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44994</v>
+        <v>45153</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,8 +8377,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8421,7 +8426,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8435,10 +8440,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45911</v>
+        <v>44589</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8451,7 +8456,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8494,7 +8499,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8508,10 +8513,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45098</v>
+        <v>44484</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8524,7 +8529,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8567,7 +8572,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8581,10 +8586,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45128</v>
+        <v>44589</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8597,7 +8602,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8640,7 +8645,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 26863-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8654,10 +8659,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45128</v>
+        <v>45810</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8670,7 +8675,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8713,7 +8718,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8723,14 +8728,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45250</v>
+        <v>45163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8743,7 +8748,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8786,7 +8791,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8800,10 +8805,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45270</v>
+        <v>45670</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,8 +8820,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>3.3</v>
+        <v>18.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8859,7 +8869,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8873,10 +8883,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44484</v>
+        <v>44965</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8889,7 +8899,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8932,7 +8942,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51659-2021</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8946,10 +8956,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44462</v>
+        <v>45342</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8962,7 +8972,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9005,7 +9015,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9019,10 +9029,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45560</v>
+        <v>45666</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9035,7 +9045,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9078,7 +9088,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9092,10 +9102,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45342</v>
+        <v>45047</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9108,7 +9118,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9151,7 +9161,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9165,10 +9175,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45769</v>
+        <v>45231</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9181,7 +9191,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9224,7 +9234,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9238,10 +9248,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46155</v>
+        <v>45554</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9253,13 +9263,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9302,7 +9307,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9316,10 +9321,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44998</v>
+        <v>45047</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9332,7 +9337,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9375,7 +9380,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9385,14 +9390,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45068</v>
+        <v>44989</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9405,7 +9410,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9448,7 +9453,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9458,14 +9463,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45174</v>
+        <v>44989</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,13 +9482,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9526,7 +9526,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 47902-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44848</v>
+        <v>45204</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9599,7 +9599,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45236</v>
+        <v>44804</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9672,7 +9672,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45973</v>
+        <v>45068</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9701,13 +9701,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9750,7 +9745,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9764,10 +9759,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46167</v>
+        <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9823,7 +9818,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9833,14 +9828,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44989</v>
+        <v>45112</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9852,8 +9847,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9906,14 +9906,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44989</v>
+        <v>45112</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9925,8 +9925,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9969,7 +9974,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9983,10 +9988,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44950</v>
+        <v>45093</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9999,7 +10004,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10042,7 +10047,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 11794-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10056,10 +10061,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45001</v>
+        <v>44994</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10072,7 +10077,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10115,7 +10120,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,10 +10134,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46174</v>
+        <v>44624</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10145,7 +10150,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>7.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10188,7 +10193,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10202,10 +10207,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46174</v>
+        <v>45069</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10218,7 +10223,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10261,7 +10266,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10275,10 +10280,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45397</v>
+        <v>44950</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10291,7 +10296,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10334,7 +10339,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10348,10 +10353,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45813</v>
+        <v>45973</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10361,6 +10366,11 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -10407,7 +10417,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10421,10 +10431,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46002</v>
+        <v>44848</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10437,7 +10447,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10480,7 +10490,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10494,10 +10504,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>44676</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10510,7 +10520,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10553,7 +10563,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10567,10 +10577,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46009</v>
+        <v>45236</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10582,13 +10592,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10631,7 +10636,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10645,10 +10650,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46009</v>
+        <v>45001</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10660,13 +10665,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10709,7 +10709,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44764</v>
+        <v>45113</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>9.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10782,7 +10782,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10796,10 +10796,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46009</v>
+        <v>44993</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10811,13 +10811,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10860,7 +10855,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10874,10 +10869,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45559</v>
+        <v>45421</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10890,7 +10885,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10933,7 +10928,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10947,10 +10942,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46031</v>
+        <v>44916</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10963,7 +10958,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11006,7 +11001,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11020,10 +11015,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46182</v>
+        <v>45553</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11035,8 +11030,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11089,14 +11089,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45331</v>
+        <v>45204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11152,7 +11152,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46190</v>
+        <v>45163</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11181,13 +11181,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11230,7 +11225,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11244,10 +11239,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46189</v>
+        <v>46031</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11259,13 +11254,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11308,7 +11298,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11322,10 +11312,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46189</v>
+        <v>46002</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11337,13 +11327,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11386,7 +11371,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11400,10 +11385,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46190</v>
+        <v>45438</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11415,13 +11400,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11464,7 +11444,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11478,10 +11458,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46189</v>
+        <v>46002</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11493,13 +11473,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>6.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11542,7 +11517,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11556,10 +11531,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46189</v>
+        <v>46009</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11573,11 +11548,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11620,7 +11595,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11634,10 +11609,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46189</v>
+        <v>45730</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11649,8 +11624,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>10.7</v>
+        <v>4.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11693,7 +11673,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11707,10 +11687,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46189</v>
+        <v>44764</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11722,13 +11702,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11771,7 +11746,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11785,10 +11760,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46191</v>
+        <v>45559</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11800,13 +11775,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11849,7 +11819,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11863,10 +11833,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46055</v>
+        <v>46009</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11878,8 +11848,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11922,7 +11897,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11936,10 +11911,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46195</v>
+        <v>45337</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11951,13 +11926,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12000,7 +11970,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12014,10 +11984,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45112</v>
+        <v>46009</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12035,7 +12005,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12078,7 +12048,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12092,10 +12062,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45014</v>
+        <v>45421</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12108,7 +12078,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>12.1</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12151,7 +12121,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12165,10 +12135,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46197</v>
+        <v>46055</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12181,7 +12151,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12224,7 +12194,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12238,10 +12208,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46197</v>
+        <v>45540</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12254,7 +12224,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12297,7 +12267,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12311,10 +12281,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45263</v>
+        <v>45523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12327,7 +12297,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12370,7 +12340,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12384,10 +12354,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46073</v>
+        <v>45523</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12400,7 +12370,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12443,7 +12413,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12457,10 +12427,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45421</v>
+        <v>45331</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12473,7 +12443,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12516,7 +12486,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12526,14 +12496,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45204</v>
+        <v>46073</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12546,7 +12516,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12589,7 +12559,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12603,10 +12573,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46199</v>
+        <v>44998</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12618,13 +12588,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12667,7 +12632,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12681,10 +12646,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46199</v>
+        <v>46244</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12702,7 +12667,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12745,7 +12710,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12759,10 +12724,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46199</v>
+        <v>44950</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12774,13 +12739,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12823,7 +12783,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12837,10 +12797,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46090</v>
+        <v>44992</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12858,7 +12818,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12901,7 +12861,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12915,10 +12875,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45740</v>
+        <v>45056</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12931,7 +12891,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12974,7 +12934,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12988,10 +12948,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45085</v>
+        <v>46090</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13003,8 +12963,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13064,7 +13029,7 @@
         <v>46090</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13125,7 +13090,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13139,10 +13104,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46202</v>
+        <v>44937</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13154,13 +13119,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13203,7 +13163,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13217,10 +13177,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45056</v>
+        <v>46101</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13233,7 +13193,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13276,7 +13236,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13290,10 +13250,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46101</v>
+        <v>45281</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13306,7 +13266,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13349,7 +13309,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13363,10 +13323,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45127</v>
+        <v>45560</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13422,7 +13382,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13436,10 +13396,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44993</v>
+        <v>45091</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13495,7 +13455,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 47902-2023</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13509,10 +13469,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45204</v>
+        <v>45001</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13525,7 +13485,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13568,7 +13528,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13582,10 +13542,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45093</v>
+        <v>46126</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13598,7 +13558,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13641,7 +13601,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13655,10 +13615,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46126</v>
+        <v>44988</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13670,8 +13630,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13714,7 +13679,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13728,10 +13693,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45281</v>
+        <v>45309</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13744,7 +13709,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13787,7 +13752,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13801,10 +13766,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44676</v>
+        <v>45840</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13817,7 +13782,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13860,7 +13825,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13874,10 +13839,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44624</v>
+        <v>45762</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13890,7 +13855,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.9</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13933,7 +13898,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13947,10 +13912,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45554</v>
+        <v>45553</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13962,8 +13927,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14006,7 +13976,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14020,10 +13990,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45523</v>
+        <v>45553</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14035,8 +14005,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14079,7 +14054,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14093,10 +14068,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45523</v>
+        <v>45241</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14109,7 +14084,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14152,7 +14127,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14166,10 +14141,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45153</v>
+        <v>45014</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14181,13 +14156,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>12.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14230,7 +14200,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14244,10 +14214,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45666</v>
+        <v>45068</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14260,7 +14230,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14303,7 +14273,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14317,10 +14287,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45113</v>
+        <v>45068</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14333,7 +14303,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14376,7 +14346,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14390,10 +14360,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44992</v>
+        <v>45616</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14405,13 +14375,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14454,7 +14419,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14464,14 +14429,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44712</v>
+        <v>44986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14484,7 +14449,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>12.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14527,7 +14492,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14541,10 +14506,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45616</v>
+        <v>45601</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14557,7 +14522,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14600,7 +14565,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14614,10 +14579,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46256</v>
+        <v>45174</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14631,11 +14596,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14678,7 +14643,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14692,10 +14657,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46256</v>
+        <v>45672</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14707,13 +14672,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14756,7 +14716,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14770,10 +14730,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45553</v>
+        <v>45646</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14785,13 +14745,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14834,7 +14789,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 61470-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14848,10 +14803,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45043</v>
+        <v>45646</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14864,7 +14819,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14907,7 +14862,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14921,10 +14876,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45483</v>
+        <v>45656</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14937,7 +14892,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14980,7 +14935,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14990,14 +14945,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46256</v>
+        <v>46155</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15015,7 +14970,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15058,7 +15013,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15068,14 +15023,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46256</v>
+        <v>45769</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15087,13 +15042,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15136,7 +15086,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15150,10 +15100,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44988</v>
+        <v>46167</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15165,13 +15115,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15214,7 +15159,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15228,10 +15173,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44804</v>
+        <v>45813</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15244,7 +15189,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15287,7 +15232,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15301,10 +15246,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46219</v>
+        <v>46174</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15317,7 +15262,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15360,7 +15305,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15374,10 +15319,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45069</v>
+        <v>46174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15390,7 +15335,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15433,7 +15378,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15447,10 +15392,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46219</v>
+        <v>46182</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15463,7 +15408,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15506,7 +15451,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15520,10 +15465,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45163</v>
+        <v>46189</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15535,8 +15480,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15579,7 +15529,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15593,10 +15543,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46219</v>
+        <v>46189</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15608,8 +15558,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15652,7 +15607,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15666,10 +15621,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45762</v>
+        <v>46189</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15681,8 +15636,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15725,7 +15685,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15739,10 +15699,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46222</v>
+        <v>46189</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15755,7 +15715,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15798,7 +15758,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15812,10 +15772,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45056</v>
+        <v>46189</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15827,8 +15787,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15871,7 +15836,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15885,10 +15850,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45553</v>
+        <v>46189</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15906,7 +15871,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15949,7 +15914,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15963,10 +15928,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45553</v>
+        <v>46191</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15980,11 +15945,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16027,7 +15992,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16041,10 +16006,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45646</v>
+        <v>46190</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16056,8 +16021,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16100,7 +16070,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16110,14 +16080,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45334</v>
+        <v>46190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16129,8 +16099,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16173,7 +16148,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16187,10 +16162,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46273</v>
+        <v>46195</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16208,7 +16183,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16251,7 +16226,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16265,10 +16240,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46273</v>
+        <v>46197</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16280,13 +16255,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16329,7 +16299,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16343,10 +16313,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46273</v>
+        <v>46197</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16358,13 +16328,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16407,7 +16372,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16421,10 +16386,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46273</v>
+        <v>46199</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16442,7 +16407,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16485,7 +16450,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16499,10 +16464,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46273</v>
+        <v>46199</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16520,7 +16485,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16563,7 +16528,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16577,10 +16542,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46273</v>
+        <v>46199</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16598,7 +16563,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16641,7 +16606,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16655,10 +16620,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46273</v>
+        <v>46202</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16676,7 +16641,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16719,7 +16684,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16729,14 +16694,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46273</v>
+        <v>46256</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16754,7 +16719,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16797,7 +16762,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16807,14 +16772,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46230</v>
+        <v>46256</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16826,8 +16791,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16870,7 +16840,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16884,10 +16854,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46273</v>
+        <v>46256</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16905,7 +16875,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16948,7 +16918,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 36996-2026</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16962,10 +16932,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46273</v>
+        <v>46256</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16983,7 +16953,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17026,7 +16996,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 36997-2026</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17040,10 +17010,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46273</v>
+        <v>46219</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17055,13 +17025,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17104,7 +17069,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17118,10 +17083,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46273</v>
+        <v>46219</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17131,11 +17096,6 @@
       <c r="G207" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -17182,7 +17142,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17196,10 +17156,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17212,7 +17172,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17255,7 +17215,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17269,10 +17229,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46273</v>
+        <v>46222</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17284,13 +17244,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17333,7 +17288,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17350,7 +17305,7 @@
         <v>46273</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17368,7 +17323,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17411,7 +17366,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17425,10 +17380,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44950</v>
+        <v>46273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17440,8 +17395,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17484,7 +17444,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17498,10 +17458,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17513,8 +17473,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17557,7 +17522,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17571,10 +17536,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45601</v>
+        <v>46273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17586,8 +17551,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17630,7 +17600,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 38021-2026</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17644,10 +17614,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17665,7 +17635,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17708,7 +17678,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17722,10 +17692,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44589</v>
+        <v>46273</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17737,8 +17707,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17781,7 +17756,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38008-2026</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17795,10 +17770,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17810,13 +17785,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17859,7 +17829,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17873,10 +17843,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44748</v>
+        <v>46230</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17889,7 +17859,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17932,7 +17902,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17942,14 +17912,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45112</v>
+        <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17967,7 +17937,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18010,7 +17980,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18024,10 +17994,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18045,7 +18015,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18088,7 +18058,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18102,10 +18072,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18117,13 +18087,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18166,7 +18131,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 61470-2024</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18180,10 +18145,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45646</v>
+        <v>46273</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18195,8 +18160,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18239,7 +18209,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18253,10 +18223,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45670</v>
+        <v>46273</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18270,11 +18240,11 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I222" t="n">
-        <v>9.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18317,7 +18287,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18331,10 +18301,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45656</v>
+        <v>46273</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18346,8 +18316,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18390,7 +18365,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 36996-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18404,10 +18379,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45600</v>
+        <v>46273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18419,8 +18394,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18463,7 +18443,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 33334-2023</t>
+          <t>A 36997-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18477,10 +18457,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45128</v>
+        <v>46273</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18492,8 +18472,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18536,7 +18521,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18550,10 +18535,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45622</v>
+        <v>46273</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18565,8 +18550,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18609,7 +18599,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 10274-2023</t>
+          <t>A 38008-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18623,10 +18613,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44986</v>
+        <v>46280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18638,8 +18628,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18682,7 +18677,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 58548-2024</t>
+          <t>A 38021-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18696,10 +18691,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45635</v>
+        <v>46280</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18711,8 +18706,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18755,24 +18755,24 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 26863-2025</t>
+          <t>S 6727-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45810</v>
+        <v>44889</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18784,8 +18784,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18828,7 +18833,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>S 6727-2022</t>
+          <t>S 6723-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18845,7 +18850,7 @@
         <v>44889</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18863,7 +18868,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18906,7 +18911,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S 6723-2022</t>
+          <t>S 231-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18920,10 +18925,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44889</v>
+        <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18941,7 +18946,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>9.6</v>
+        <v>1.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18984,7 +18989,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S 231-2024</t>
+          <t>S 1250-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18998,10 +19003,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45317</v>
+        <v>45762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19019,7 +19024,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19062,7 +19067,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 1250-2025</t>
+          <t>S 26-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19072,14 +19077,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45762</v>
+        <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19091,13 +19096,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>1.2</v>
+        <v>13.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19140,7 +19140,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 26-2026</t>
+          <t>S 505-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19150,14 +19150,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46030</v>
+        <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19213,7 +19213,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 505-2026</t>
+          <t>S 2206-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19227,10 +19227,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46076</v>
+        <v>46256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19242,8 +19242,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19283,10 +19288,10 @@
       </c>
       <c r="V235" s="2" t="inlineStr"/>
     </row>
-    <row r="236" ht="15" customHeight="1">
+    <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 2206-2026</t>
+          <t>S 2205-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19303,7 +19308,7 @@
         <v>46256</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19321,7 +19326,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19360,84 +19365,6 @@
         <v>0</v>
       </c>
       <c r="V236" s="2" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>S 2205-2026</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D237" s="1" t="n">
-        <v>46256</v>
-      </c>
-      <c r="E237" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I237" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J237" t="n">
-        <v>0</v>
-      </c>
-      <c r="K237" t="n">
-        <v>0</v>
-      </c>
-      <c r="L237" t="n">
-        <v>0</v>
-      </c>
-      <c r="M237" t="n">
-        <v>0</v>
-      </c>
-      <c r="N237" t="n">
-        <v>0</v>
-      </c>
-      <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="P237" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
-      <c r="S237" t="n">
-        <v>0</v>
-      </c>
-      <c r="T237" t="n">
-        <v>0</v>
-      </c>
-      <c r="U237" t="n">
-        <v>0</v>
-      </c>
-      <c r="V237" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 28147-2022</t>
+          <t>A 27395-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44746</v>
+        <v>46189</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -749,23 +749,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -777,18 +782,134 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
       </c>
       <c r="T3" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Entita
+Grantaggsvamp
+Talltita
+Vedticka
+Spillkråka
+Tofsmes
+Smålom</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 28147-2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
         <v>15</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre hackspett
@@ -800,157 +921,36 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 27395-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>16</v>
-      </c>
-      <c r="U4" t="n">
-        <v>16</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Entita
-Grantaggsvamp
-Talltita
-Vedticka
-Spillkråka
-Tofsmes
-Smålom</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
         <v/>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 33104-2024</t>
+          <t>A 24919-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45517</v>
+        <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1233,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1245,9 +1245,341 @@
         <v>4</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Svinrot
+Mattlummer
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 24919-2026 artfynd.xlsx", "A 24919-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 24919-2026 karta.png", "A 24919-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 24919-2026 georefererad karta.tif", "A 24919-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 24919-2026 FSC-klagomål.docx", "A 24919-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 24919-2026 FSC-klagomål mail.docx", "A 24919-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 24919-2026 tillsynsbegäran.docx", "A 24919-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 24919-2026 tillsynsbegäran mail.docx", "A 24919-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4468-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44589</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka
+Tjäder
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 4468-2022 artfynd.xlsx", "A 4468-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 4468-2022 karta.png", "A 4468-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 4468-2022 georefererad karta.tif", "A 4468-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 4468-2022 FSC-klagomål.docx", "A 4468-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 4468-2022 FSC-klagomål mail.docx", "A 4468-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 4468-2022 tillsynsbegäran.docx", "A 4468-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 4468-2022 tillsynsbegäran mail.docx", "A 4468-2022")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 4468-2022 prioriterade fågelarter.docx", "A 4468-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 31357-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka
+Tjäder
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 31357-2026 artfynd.xlsx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 31357-2026 karta.png", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 31357-2026 georefererad karta.tif", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 31357-2026 FSC-klagomål.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 31357-2026 FSC-klagomål mail.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 31357-2026 tillsynsbegäran.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 31357-2026 tillsynsbegäran mail.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 31357-2026 prioriterade fågelarter.docx", "A 31357-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 33104-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45517</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Blekspindling agg.
@@ -1255,368 +1587,36 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33104-2024 artfynd.xlsx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33104-2024 karta.png", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33104-2024 georefererad karta.tif", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 33104-2024 karta knärot.png", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33104-2024 FSC-klagomål.docx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33104-2024 FSC-klagomål mail.docx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33104-2024 tillsynsbegäran.docx", "A 33104-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33104-2024 tillsynsbegäran mail.docx", "A 33104-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 24919-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot
-Mattlummer
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 24919-2026 artfynd.xlsx", "A 24919-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 24919-2026 karta.png", "A 24919-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 24919-2026 georefererad karta.tif", "A 24919-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 24919-2026 FSC-klagomål.docx", "A 24919-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 24919-2026 FSC-klagomål mail.docx", "A 24919-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 24919-2026 tillsynsbegäran.docx", "A 24919-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 24919-2026 tillsynsbegäran mail.docx", "A 24919-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 4468-2022</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44589</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>12</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka
-Tjäder
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 4468-2022 artfynd.xlsx", "A 4468-2022")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 4468-2022 karta.png", "A 4468-2022")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 4468-2022 georefererad karta.tif", "A 4468-2022")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 4468-2022 FSC-klagomål.docx", "A 4468-2022")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 4468-2022 FSC-klagomål mail.docx", "A 4468-2022")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 4468-2022 tillsynsbegäran.docx", "A 4468-2022")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 4468-2022 tillsynsbegäran mail.docx", "A 4468-2022")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 4468-2022 prioriterade fågelarter.docx", "A 4468-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31357-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>11</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka
-Tjäder
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 31357-2026 artfynd.xlsx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 31357-2026 karta.png", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 31357-2026 georefererad karta.tif", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 31357-2026 FSC-klagomål.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 31357-2026 FSC-klagomål mail.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 31357-2026 tillsynsbegäran.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 31357-2026 tillsynsbegäran mail.docx", "A 31357-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 31357-2026 prioriterade fågelarter.docx", "A 31357-2026")</f>
         <v/>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45368</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44539</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37012-2022</t>
+          <t>A 11637-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44806</v>
+        <v>45727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1977,23 +1977,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2011,804 +2016,799 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 11278-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 15523-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Thymalus limbatus
+Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 37012-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44806</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>10</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 11278-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46080</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 35099-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 35099-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45852</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 15523-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S 765-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="I21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Thymalus limbatus
-Vanlig flatbagge</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 11637-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 27240-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S 765-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Rävticka</t>
-        </is>
-      </c>
       <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/S 765-2025 artfynd.xlsx", "S 765-2025")</f>
         <v/>
@@ -2858,7 +2858,7 @@
         <v>46052</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45305</v>
+        <v>45042</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3122,46 +3122,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3175,10 +3171,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45393</v>
+        <v>45447</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3191,7 +3187,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3224,49 +3220,53 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45127</v>
+        <v>45362</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3332,46 +3332,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 44857-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3385,10 +3389,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45559</v>
+        <v>45918</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3401,7 +3405,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3441,42 +3445,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12550-2026</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3490,10 +3494,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46090</v>
+        <v>45393</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3505,13 +3509,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3547,46 +3546,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12557-2026</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3600,10 +3599,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46090</v>
+        <v>45559</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3615,23 +3614,18 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3645,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3661,42 +3655,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 12550-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3710,10 +3704,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45042</v>
+        <v>46090</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3725,8 +3719,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3770,38 +3769,38 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 12557-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3815,10 +3814,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45447</v>
+        <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3830,14 +3829,19 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3864,53 +3868,49 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45362</v>
+        <v>45127</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3976,43 +3976,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
@@ -4036,7 +4032,7 @@
         <v>45656</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4124,7 +4120,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44857-2025</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4138,10 +4134,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45918</v>
+        <v>45305</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4154,16 +4150,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4178,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4190,39 +4186,43 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44601</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44656</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44519</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44508</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44734</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44609</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44830</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44632</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44488</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44748</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 5043-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44796</v>
+        <v>44593</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5627,7 +5627,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 45105-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45600</v>
+        <v>44843</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5700,7 +5700,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 8050-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45085</v>
+        <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5043-2022</t>
+          <t>A 67508-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44593</v>
+        <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 41979-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44824</v>
+        <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5875,8 +5875,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5919,7 +5924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 67508-2021</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5933,10 +5938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44524</v>
+        <v>44824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5949,7 +5954,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5992,7 +5997,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41979-2022</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6006,10 +6011,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44830</v>
+        <v>44589</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6019,11 +6024,6 @@
       <c r="G58" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -6070,7 +6070,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45105-2022</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44843</v>
+        <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33334-2023</t>
+          <t>A 11676-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45128</v>
+        <v>45373</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45483</v>
+        <v>44937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44748</v>
+        <v>44479</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8050-2022</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44609</v>
+        <v>44796</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45670</v>
+        <v>45093</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6464,13 +6464,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>9.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6513,7 +6508,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6527,10 +6522,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45127</v>
+        <v>45540</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6543,7 +6538,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6586,7 +6581,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6600,10 +6595,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44839</v>
+        <v>45553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6615,8 +6610,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45270</v>
+        <v>45438</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45539</v>
+        <v>45001</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6805,7 +6805,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45622</v>
+        <v>45309</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45553</v>
+        <v>45134</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6907,13 +6907,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6956,7 +6951,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6970,10 +6965,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45093</v>
+        <v>45163</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,7 +6981,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7029,7 +7024,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10274-2023</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7043,10 +7038,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44986</v>
+        <v>45421</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7059,7 +7054,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7102,7 +7097,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7116,10 +7111,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44479</v>
+        <v>45231</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7132,7 +7127,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7175,7 +7170,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7189,10 +7184,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45553</v>
+        <v>45730</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7206,11 +7201,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7253,7 +7248,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11676-2024</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7267,10 +7262,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45373</v>
+        <v>45241</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7283,7 +7278,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7326,7 +7321,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58548-2024</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7340,10 +7335,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45635</v>
+        <v>45539</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7356,7 +7351,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7399,7 +7394,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7413,10 +7408,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45056</v>
+        <v>45047</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7429,7 +7424,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7472,7 +7467,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7486,10 +7481,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45740</v>
+        <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7502,7 +7497,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7545,7 +7540,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7559,10 +7554,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45740</v>
+        <v>45047</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7575,7 +7570,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7618,7 +7613,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7632,10 +7627,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45250</v>
+        <v>44986</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7648,7 +7643,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.2</v>
+        <v>12.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7691,7 +7686,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7705,10 +7700,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45397</v>
+        <v>45091</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7721,7 +7716,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7764,7 +7759,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7778,10 +7773,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45128</v>
+        <v>45337</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7794,7 +7789,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7837,7 +7832,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7851,10 +7846,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45128</v>
+        <v>45840</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7867,7 +7862,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7910,7 +7905,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7924,10 +7919,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45263</v>
+        <v>45672</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7940,7 +7935,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7983,7 +7978,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7997,10 +7992,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45134</v>
+        <v>45068</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8013,7 +8008,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8056,7 +8051,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8070,10 +8065,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45098</v>
+        <v>45068</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8086,7 +8081,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8129,7 +8124,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8139,14 +8134,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45334</v>
+        <v>45740</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8159,7 +8154,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8202,7 +8197,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8216,10 +8211,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45911</v>
+        <v>45670</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8231,8 +8226,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>18.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45043</v>
+        <v>44839</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 11794-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45153</v>
+        <v>44994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,13 +8377,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8426,7 +8421,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8440,10 +8435,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44589</v>
+        <v>45911</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8456,7 +8451,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8499,7 +8494,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8513,10 +8508,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44484</v>
+        <v>45098</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8529,7 +8524,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8572,7 +8567,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8586,10 +8581,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44589</v>
+        <v>45128</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8602,7 +8597,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8645,7 +8640,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26863-2025</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8659,10 +8654,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45810</v>
+        <v>45128</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8675,7 +8670,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8718,7 +8713,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8728,14 +8723,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45163</v>
+        <v>45250</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8748,7 +8743,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8791,7 +8786,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8805,10 +8800,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45670</v>
+        <v>45270</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8820,13 +8815,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>18.8</v>
+        <v>3.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8869,7 +8859,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8883,10 +8873,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44965</v>
+        <v>44484</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8899,7 +8889,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8942,7 +8932,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8956,10 +8946,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45342</v>
+        <v>45560</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8972,7 +8962,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9015,7 +9005,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9029,10 +9019,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45666</v>
+        <v>45342</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9045,7 +9035,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9088,7 +9078,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9102,10 +9092,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45047</v>
+        <v>44998</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9118,7 +9108,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9161,7 +9151,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9171,14 +9161,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45231</v>
+        <v>45068</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9191,7 +9181,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9234,7 +9224,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9248,10 +9238,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45554</v>
+        <v>45174</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9263,8 +9253,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9307,7 +9302,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9321,10 +9316,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45047</v>
+        <v>44848</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9380,7 +9375,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9390,14 +9385,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44989</v>
+        <v>45236</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9410,7 +9405,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9453,7 +9448,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9463,14 +9458,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44989</v>
+        <v>45973</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9482,8 +9477,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9526,7 +9526,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47902-2023</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9536,14 +9536,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45204</v>
+        <v>44989</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9599,7 +9599,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9609,14 +9609,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44804</v>
+        <v>44989</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9672,7 +9672,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45068</v>
+        <v>44950</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9745,7 +9745,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44712</v>
+        <v>45001</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45112</v>
+        <v>45397</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9847,13 +9847,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9896,7 +9891,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9906,14 +9901,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45112</v>
+        <v>45769</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9925,13 +9920,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9974,7 +9964,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9988,10 +9978,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45093</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10004,7 +9994,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10047,7 +10037,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 11794-2023</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10061,10 +10051,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44994</v>
+        <v>46002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10077,7 +10067,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10120,7 +10110,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10134,10 +10124,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44624</v>
+        <v>44764</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10150,7 +10140,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10193,7 +10183,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10207,10 +10197,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45069</v>
+        <v>46155</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10222,8 +10212,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10266,7 +10261,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10280,10 +10275,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44950</v>
+        <v>46009</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10295,8 +10290,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10339,7 +10339,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10353,10 +10353,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45973</v>
+        <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10370,11 +10370,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10417,7 +10417,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10431,10 +10431,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44848</v>
+        <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10446,8 +10446,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10490,7 +10495,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10504,10 +10509,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44676</v>
+        <v>45559</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10520,7 +10525,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10563,7 +10568,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10577,10 +10582,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45236</v>
+        <v>46031</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10593,7 +10598,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10636,7 +10641,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10650,10 +10655,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45001</v>
+        <v>45331</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10666,7 +10671,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10709,7 +10714,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10723,10 +10728,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45113</v>
+        <v>46167</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10739,7 +10744,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10782,7 +10787,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10796,10 +10801,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44993</v>
+        <v>45112</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10811,8 +10816,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10855,7 +10865,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10869,10 +10879,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45421</v>
+        <v>46055</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10885,7 +10895,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10928,7 +10938,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10942,10 +10952,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44916</v>
+        <v>45014</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10958,7 +10968,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.9</v>
+        <v>12.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11001,7 +11011,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11015,10 +11025,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45553</v>
+        <v>45263</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11030,13 +11040,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11079,7 +11084,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11089,14 +11094,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45204</v>
+        <v>45421</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11109,7 +11114,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11152,7 +11157,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11162,14 +11167,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45163</v>
+        <v>45204</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11182,7 +11187,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11225,7 +11230,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11239,10 +11244,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46031</v>
+        <v>45740</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11255,7 +11260,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11298,7 +11303,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46002</v>
+        <v>45085</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11328,7 +11333,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11371,7 +11376,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11385,10 +11390,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45438</v>
+        <v>46073</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11401,7 +11406,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11444,7 +11449,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11458,10 +11463,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46002</v>
+        <v>45056</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11474,7 +11479,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11517,7 +11522,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11531,10 +11536,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46009</v>
+        <v>46174</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11546,13 +11551,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11595,7 +11595,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45730</v>
+        <v>46174</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11624,13 +11624,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11673,7 +11668,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11687,10 +11682,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44764</v>
+        <v>45813</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11703,7 +11698,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>9.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11746,7 +11741,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11760,10 +11755,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45559</v>
+        <v>46090</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,8 +11770,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11819,7 +11819,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 12547-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11833,10 +11833,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46009</v>
+        <v>46090</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11850,11 +11850,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11897,7 +11897,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11911,10 +11911,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45337</v>
+        <v>45127</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11970,7 +11970,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11984,10 +11984,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46009</v>
+        <v>46101</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11999,13 +11999,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12048,7 +12043,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12062,10 +12057,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45421</v>
+        <v>46182</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12078,7 +12073,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12121,7 +12116,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12135,10 +12130,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46055</v>
+        <v>44993</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12151,7 +12146,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12194,7 +12189,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 47902-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12208,10 +12203,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45540</v>
+        <v>45204</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12224,7 +12219,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12267,7 +12262,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12281,10 +12276,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45523</v>
+        <v>45093</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12297,7 +12292,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12340,7 +12335,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12354,10 +12349,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45523</v>
+        <v>46190</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12369,8 +12364,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12413,7 +12413,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12427,10 +12427,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45331</v>
+        <v>46189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12442,8 +12442,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12486,7 +12491,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12500,10 +12505,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46073</v>
+        <v>45281</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12516,7 +12521,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12559,7 +12564,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12573,10 +12578,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44998</v>
+        <v>46189</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12588,8 +12593,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12632,7 +12642,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12646,10 +12656,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46244</v>
+        <v>46190</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12667,7 +12677,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12710,7 +12720,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12724,10 +12734,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44950</v>
+        <v>46189</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12739,8 +12749,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12783,7 +12798,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12797,10 +12812,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44992</v>
+        <v>46189</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12818,7 +12833,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12861,7 +12876,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12875,10 +12890,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45056</v>
+        <v>46189</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12891,7 +12906,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12934,7 +12949,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12948,10 +12963,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46090</v>
+        <v>46189</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13012,7 +13027,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12547-2026</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13026,10 +13041,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46090</v>
+        <v>44676</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13041,13 +13056,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13090,7 +13100,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13104,10 +13114,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44937</v>
+        <v>46126</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13120,7 +13130,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13163,7 +13173,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13177,10 +13187,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46101</v>
+        <v>44624</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13193,7 +13203,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13236,7 +13246,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13250,10 +13260,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45281</v>
+        <v>46191</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13265,8 +13275,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13309,7 +13324,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13323,10 +13338,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45560</v>
+        <v>45554</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13339,7 +13354,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13382,7 +13397,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13396,10 +13411,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45091</v>
+        <v>45523</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13412,7 +13427,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13455,7 +13470,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13469,10 +13484,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45001</v>
+        <v>45523</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13485,7 +13500,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13528,7 +13543,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13542,10 +13557,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46126</v>
+        <v>46195</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13557,8 +13572,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13601,7 +13621,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13615,10 +13635,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44988</v>
+        <v>45153</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13636,7 +13656,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13679,7 +13699,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13693,10 +13713,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45309</v>
+        <v>45666</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13709,7 +13729,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13752,7 +13772,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13766,10 +13786,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45840</v>
+        <v>45113</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13782,7 +13802,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13825,7 +13845,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13839,10 +13859,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45762</v>
+        <v>46197</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13855,7 +13875,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13898,7 +13918,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13912,10 +13932,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45553</v>
+        <v>46197</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13927,13 +13947,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13976,7 +13991,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13990,10 +14005,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45553</v>
+        <v>44992</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14011,7 +14026,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14054,7 +14069,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14068,10 +14083,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45241</v>
+        <v>46199</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14083,8 +14098,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14127,7 +14147,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14141,10 +14161,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45014</v>
+        <v>46199</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14156,8 +14176,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>12.1</v>
+        <v>9.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14200,7 +14225,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14214,10 +14239,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45068</v>
+        <v>46199</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14229,8 +14254,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14273,7 +14303,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14287,10 +14317,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45068</v>
+        <v>44712</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14303,7 +14333,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14346,7 +14376,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14360,10 +14390,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45616</v>
+        <v>46202</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14375,8 +14405,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14419,7 +14454,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14429,14 +14464,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44986</v>
+        <v>45616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14449,7 +14484,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>12.8</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14492,7 +14527,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14506,10 +14541,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45601</v>
+        <v>45553</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14521,8 +14556,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14565,7 +14605,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14579,10 +14619,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45174</v>
+        <v>45043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14594,13 +14634,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14643,7 +14678,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14657,10 +14692,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45672</v>
+        <v>45483</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14673,7 +14708,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14716,7 +14751,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14730,10 +14765,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45646</v>
+        <v>44988</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14745,8 +14780,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14789,7 +14829,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 61470-2024</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14803,10 +14843,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45646</v>
+        <v>44804</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14819,7 +14859,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14862,7 +14902,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14876,10 +14916,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45656</v>
+        <v>45069</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14892,7 +14932,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14935,7 +14975,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14949,10 +14989,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46155</v>
+        <v>45163</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14964,13 +15004,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15013,7 +15048,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15027,10 +15062,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45769</v>
+        <v>45762</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15043,7 +15078,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15086,7 +15121,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15100,10 +15135,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46167</v>
+        <v>45056</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15116,7 +15151,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15159,7 +15194,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15173,10 +15208,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45813</v>
+        <v>45553</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15188,8 +15223,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15232,7 +15272,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15246,10 +15286,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46174</v>
+        <v>45553</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15261,8 +15301,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15305,7 +15350,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15319,10 +15364,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46174</v>
+        <v>45646</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15335,7 +15380,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15378,7 +15423,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15388,14 +15433,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46182</v>
+        <v>45334</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15408,7 +15453,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15451,7 +15496,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15465,10 +15510,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46189</v>
+        <v>46256</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15486,7 +15531,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15529,7 +15574,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15543,10 +15588,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46189</v>
+        <v>46256</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15564,7 +15609,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15607,7 +15652,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15617,14 +15662,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46189</v>
+        <v>46256</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15642,7 +15687,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15685,7 +15730,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15695,14 +15740,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46189</v>
+        <v>46256</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15714,8 +15759,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>10.7</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15758,7 +15808,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15772,10 +15822,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46189</v>
+        <v>44950</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15787,13 +15837,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15836,7 +15881,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15850,10 +15895,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15865,13 +15910,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15914,7 +15954,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15928,10 +15968,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46191</v>
+        <v>46219</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15943,13 +15983,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15992,7 +16027,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16006,10 +16041,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46190</v>
+        <v>46219</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16021,13 +16056,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16070,7 +16100,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16084,10 +16114,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46190</v>
+        <v>46222</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16099,13 +16129,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16148,7 +16173,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16162,10 +16187,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46195</v>
+        <v>45601</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16177,13 +16202,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16226,7 +16246,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16240,10 +16260,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46197</v>
+        <v>44589</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16256,7 +16276,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16299,7 +16319,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16313,10 +16333,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46197</v>
+        <v>46273</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16328,8 +16348,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16372,7 +16397,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16386,10 +16411,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46199</v>
+        <v>44748</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16401,13 +16426,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16450,7 +16470,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16464,10 +16484,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16485,7 +16505,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16528,7 +16548,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16542,10 +16562,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16563,7 +16583,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16606,7 +16626,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16620,10 +16640,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46202</v>
+        <v>46273</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16641,7 +16661,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16684,7 +16704,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16694,14 +16714,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16719,7 +16739,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16762,7 +16782,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16772,14 +16792,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16797,7 +16817,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16840,7 +16860,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16854,10 +16874,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16875,7 +16895,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16918,7 +16938,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16932,10 +16952,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16953,7 +16973,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16996,7 +17016,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17010,10 +17030,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46219</v>
+        <v>46230</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17026,7 +17046,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17069,7 +17089,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17083,10 +17103,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46219</v>
+        <v>46273</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17098,8 +17118,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17142,7 +17167,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 36996-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17156,10 +17181,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46219</v>
+        <v>46273</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17171,8 +17196,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17215,7 +17245,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 36997-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17229,10 +17259,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46222</v>
+        <v>46273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17244,8 +17274,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17288,7 +17323,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17305,7 +17340,7 @@
         <v>46273</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17323,7 +17358,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17366,7 +17401,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17380,10 +17415,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46273</v>
+        <v>46230</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17395,13 +17430,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17444,7 +17474,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17461,7 +17491,7 @@
         <v>46273</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17479,7 +17509,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17522,7 +17552,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17539,7 +17569,7 @@
         <v>46273</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17557,7 +17587,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17600,7 +17630,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17610,14 +17640,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46273</v>
+        <v>45112</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17635,7 +17665,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17678,7 +17708,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17692,10 +17722,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17707,13 +17737,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17756,7 +17781,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17770,10 +17795,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46274</v>
+        <v>45553</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17785,8 +17810,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17829,7 +17859,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 38021-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17843,10 +17873,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46230</v>
+        <v>46280</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17858,8 +17888,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17902,7 +17937,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 38008-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17916,10 +17951,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17937,7 +17972,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17980,7 +18015,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 61470-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17994,10 +18029,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46273</v>
+        <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18009,13 +18044,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18058,7 +18088,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18072,10 +18102,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46230</v>
+        <v>45670</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18087,8 +18117,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>1.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18131,7 +18166,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18145,10 +18180,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46273</v>
+        <v>46244</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18166,7 +18201,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18209,7 +18244,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18223,10 +18258,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46273</v>
+        <v>45656</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18236,11 +18271,6 @@
       <c r="G222" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I222" t="n">
@@ -18287,7 +18317,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18301,10 +18331,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46273</v>
+        <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18316,13 +18346,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18365,7 +18390,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 36996-2026</t>
+          <t>A 33334-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18379,10 +18404,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46273</v>
+        <v>45128</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18394,13 +18419,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18443,7 +18463,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 36997-2026</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18457,10 +18477,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46273</v>
+        <v>45622</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18472,13 +18492,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18521,7 +18536,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 10274-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18535,10 +18550,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46273</v>
+        <v>44986</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18550,13 +18565,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18599,7 +18609,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 38008-2026</t>
+          <t>A 58548-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18613,10 +18623,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46280</v>
+        <v>45635</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18628,13 +18638,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18677,7 +18682,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 38021-2026</t>
+          <t>A 26863-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18691,10 +18696,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46280</v>
+        <v>45810</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18706,13 +18711,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18772,7 +18772,7 @@
         <v>44889</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>44889</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>46256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46256</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 27395-2026</t>
+          <t>A 28147-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46189</v>
+        <v>44746</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -749,28 +749,23 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -782,18 +777,139 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
       </c>
       <c r="T3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre hackspett
+Nötkråka
+Ullticka
+Grön sköldmossa
+Hasselsopp
+Stubbspretmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 27395-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
         <v>16</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>16</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Entita
@@ -805,152 +921,36 @@
 Smålom</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 28147-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre hackspett
-Nötkråka
-Ullticka
-Grön sköldmossa
-Hasselsopp
-Stubbspretmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
         <v/>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>44589</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45368</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44539</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11637-2025</t>
+          <t>A 11278-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45727</v>
+        <v>46080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1977,28 +1977,23 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2010,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2019,711 +2014,716 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 15523-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Thymalus limbatus
+Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 35099-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 37012-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44806</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 11637-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 11278-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46080</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27240-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 15523-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Thymalus limbatus
-Vanlig flatbagge</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 37012-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44806</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>10</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 35099-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45852</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
         <v/>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
         <v>45727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>46052</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45042</v>
+        <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3118,46 +3118,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45447</v>
+        <v>45127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3220,53 +3220,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 12550-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3280,10 +3276,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45362</v>
+        <v>46090</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3295,8 +3291,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3336,46 +3337,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44857-2025</t>
+          <t>A 12557-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3389,10 +3386,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45918</v>
+        <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3404,17 +3401,22 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3429,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3445,42 +3447,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3494,10 +3496,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45393</v>
+        <v>45559</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3510,17 +3512,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3534,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3550,42 +3552,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3599,10 +3601,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45559</v>
+        <v>45305</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3615,16 +3617,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3639,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3651,46 +3653,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12550-2026</t>
+          <t>A 44857-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3704,10 +3710,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46090</v>
+        <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3719,23 +3725,18 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3749,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3761,46 +3762,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12557-2026</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3814,10 +3815,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>45042</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,19 +3830,14 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3871,46 +3867,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3924,10 +3920,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45127</v>
+        <v>45447</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3940,7 +3936,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3973,49 +3969,53 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 290-2025</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45656</v>
+        <v>45362</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4085,42 +4085,46 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 290-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4134,10 +4138,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45305</v>
+        <v>45656</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4150,13 +4154,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4190,39 +4194,35 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
         <v/>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44601</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44656</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44519</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44508</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44734</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44609</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44830</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44632</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44488</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44748</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44593</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44843</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44824</v>
+        <v>45483</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44589</v>
+        <v>44839</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44916</v>
+        <v>45553</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6099,8 +6099,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6143,7 +6148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11676-2024</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6157,10 +6162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45373</v>
+        <v>45093</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6173,7 +6178,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6216,7 +6221,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 11676-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6230,10 +6235,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44937</v>
+        <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6246,7 +6251,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6289,7 +6294,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6303,10 +6308,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44479</v>
+        <v>45056</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6319,7 +6324,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6362,7 +6367,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6372,14 +6377,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44796</v>
+        <v>45250</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6392,7 +6397,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6435,7 +6440,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6449,10 +6454,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45093</v>
+        <v>45397</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6465,7 +6470,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6508,7 +6513,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 10274-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6522,10 +6527,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45540</v>
+        <v>44986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6538,7 +6543,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6581,7 +6586,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6595,10 +6600,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45553</v>
+        <v>45263</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6610,13 +6615,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45438</v>
+        <v>45134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 58548-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45001</v>
+        <v>45635</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6805,7 +6805,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6815,14 +6815,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45309</v>
+        <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45134</v>
+        <v>46031</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>12</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45163</v>
+        <v>45740</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45421</v>
+        <v>45043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45231</v>
+        <v>44589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7170,7 +7170,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45730</v>
+        <v>44484</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7199,13 +7199,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7248,7 +7243,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7262,10 +7257,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45241</v>
+        <v>45670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7277,8 +7272,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>6.8</v>
+        <v>18.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7321,7 +7321,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45539</v>
+        <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7394,7 +7394,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45047</v>
+        <v>45911</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7467,7 +7467,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44965</v>
+        <v>45666</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7540,7 +7540,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45047</v>
+        <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7613,7 +7613,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7623,14 +7623,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44986</v>
+        <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>12.8</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7686,7 +7686,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7700,10 +7700,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45091</v>
+        <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7759,7 +7759,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45337</v>
+        <v>45047</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7832,7 +7832,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 26863-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45840</v>
+        <v>45810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7905,7 +7905,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45672</v>
+        <v>46090</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,8 +7934,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7978,7 +7983,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 12547-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7992,10 +7997,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45068</v>
+        <v>46090</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8007,8 +8012,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8051,7 +8061,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8061,14 +8071,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
         <v>45068</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8081,7 +8091,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8124,7 +8134,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8138,10 +8148,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45740</v>
+        <v>46101</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8154,7 +8164,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8197,7 +8207,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8211,10 +8221,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45670</v>
+        <v>45112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8232,7 +8242,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>18.8</v>
+        <v>3.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8275,7 +8285,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8285,14 +8295,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44839</v>
+        <v>45112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8304,8 +8314,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8365,7 +8380,7 @@
         <v>44994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8421,7 +8436,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8435,10 +8450,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45911</v>
+        <v>44950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8451,7 +8466,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8494,7 +8509,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8508,10 +8523,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45098</v>
+        <v>46126</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8524,7 +8539,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8567,7 +8582,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8581,10 +8596,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45128</v>
+        <v>45236</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8597,7 +8612,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8640,7 +8655,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8654,10 +8669,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45128</v>
+        <v>45973</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,8 +8684,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8713,7 +8733,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8723,14 +8743,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45250</v>
+        <v>45001</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8743,7 +8763,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8786,7 +8806,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8800,10 +8820,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45270</v>
+        <v>45113</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8816,7 +8836,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8859,7 +8879,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8873,10 +8893,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44484</v>
+        <v>44993</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8889,7 +8909,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8932,7 +8952,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8946,10 +8966,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45560</v>
+        <v>44916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8962,7 +8982,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9005,7 +9025,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9019,10 +9039,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45342</v>
+        <v>45553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9034,8 +9054,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9078,7 +9103,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9088,14 +9113,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44998</v>
+        <v>45204</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9108,7 +9133,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9151,7 +9176,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9161,14 +9186,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45068</v>
+        <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9181,7 +9206,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9224,7 +9249,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9238,10 +9263,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45174</v>
+        <v>45840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9253,13 +9278,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9302,7 +9322,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9316,10 +9336,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44848</v>
+        <v>44796</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9332,7 +9352,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9375,7 +9395,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9389,10 +9409,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45236</v>
+        <v>45085</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9405,7 +9425,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9448,7 +9468,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9462,10 +9482,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,13 +9497,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9526,7 +9541,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9536,14 +9551,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44989</v>
+        <v>44824</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9556,7 +9571,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9599,7 +9614,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9609,14 +9624,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44989</v>
+        <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9629,7 +9644,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9672,7 +9687,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9686,10 +9701,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44950</v>
+        <v>44748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9702,7 +9717,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9745,7 +9760,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9759,10 +9774,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45001</v>
+        <v>46009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9774,8 +9789,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9818,7 +9838,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9832,10 +9852,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45397</v>
+        <v>45559</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9848,7 +9868,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9891,7 +9911,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9905,10 +9925,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45769</v>
+        <v>46009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,8 +9940,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9964,7 +9989,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9978,10 +10003,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,8 +10018,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10037,7 +10067,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10051,10 +10081,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46002</v>
+        <v>45127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10067,7 +10097,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10110,7 +10140,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10124,10 +10154,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44764</v>
+        <v>45270</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10140,7 +10170,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>9.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10183,7 +10213,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10197,10 +10227,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46155</v>
+        <v>45539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,13 +10242,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10261,7 +10286,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10275,10 +10300,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46009</v>
+        <v>44479</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10290,13 +10315,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10339,7 +10359,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10353,10 +10373,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46009</v>
+        <v>45553</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10370,7 +10390,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -10417,7 +10437,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10431,10 +10451,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46009</v>
+        <v>46155</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10448,11 +10468,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10495,7 +10515,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10509,10 +10529,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45559</v>
+        <v>45769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10525,7 +10545,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10568,7 +10588,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10582,10 +10602,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46031</v>
+        <v>45740</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10598,7 +10618,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10641,7 +10661,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10655,10 +10675,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45331</v>
+        <v>45128</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10671,7 +10691,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10714,7 +10734,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10728,10 +10748,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46167</v>
+        <v>45128</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10744,7 +10764,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10787,7 +10807,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10801,10 +10821,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45112</v>
+        <v>46167</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10816,13 +10836,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10865,7 +10880,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10879,10 +10894,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46055</v>
+        <v>45098</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10895,7 +10910,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10938,7 +10953,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10952,10 +10967,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45014</v>
+        <v>45813</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10968,7 +10983,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>12.1</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11011,7 +11026,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11025,10 +11040,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45263</v>
+        <v>46174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11041,7 +11056,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11084,7 +11099,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11098,10 +11113,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45421</v>
+        <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11114,7 +11129,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11157,7 +11172,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11167,14 +11182,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45204</v>
+        <v>45153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11186,8 +11201,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11230,7 +11250,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11244,10 +11264,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45740</v>
+        <v>44589</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11260,7 +11280,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11303,7 +11323,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11317,10 +11337,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45085</v>
+        <v>45163</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11333,7 +11353,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11376,7 +11396,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11390,10 +11410,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46073</v>
+        <v>46182</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11406,7 +11426,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11449,7 +11469,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11463,10 +11483,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45056</v>
+        <v>44965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11479,7 +11499,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11522,7 +11542,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11536,10 +11556,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46174</v>
+        <v>45342</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11552,7 +11572,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11595,7 +11615,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11609,10 +11629,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46174</v>
+        <v>46189</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11624,8 +11644,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11668,7 +11693,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11682,10 +11707,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45813</v>
+        <v>46189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11697,8 +11722,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11741,7 +11771,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11755,10 +11785,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46090</v>
+        <v>46189</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11776,7 +11806,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11819,7 +11849,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12547-2026</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11833,10 +11863,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46090</v>
+        <v>46189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11848,13 +11878,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3.1</v>
+        <v>10.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11897,7 +11922,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11911,10 +11936,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45127</v>
+        <v>46189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11926,8 +11951,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11970,7 +12000,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11984,10 +12014,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46101</v>
+        <v>46189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11999,8 +12029,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12043,7 +12078,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12057,10 +12092,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46182</v>
+        <v>45047</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12073,7 +12108,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12116,7 +12151,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12130,10 +12165,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44993</v>
+        <v>46191</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12145,8 +12180,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12189,7 +12229,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 47902-2023</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12203,10 +12243,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45204</v>
+        <v>46190</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12218,8 +12258,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12262,7 +12307,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12276,10 +12321,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45093</v>
+        <v>46190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12291,8 +12336,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12335,7 +12385,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12349,10 +12399,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12370,7 +12420,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12413,7 +12463,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12427,10 +12477,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46189</v>
+        <v>46197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12442,13 +12492,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12491,7 +12536,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12505,10 +12550,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45281</v>
+        <v>46197</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12521,7 +12566,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12564,7 +12609,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12578,10 +12623,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12599,7 +12644,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12642,7 +12687,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12656,10 +12701,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12677,7 +12722,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12720,7 +12765,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12734,10 +12779,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12755,7 +12800,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12798,7 +12843,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12812,10 +12857,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46189</v>
+        <v>46202</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12833,7 +12878,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12876,7 +12921,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12886,14 +12931,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46189</v>
+        <v>44989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12906,7 +12951,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>10.7</v>
+        <v>5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12949,7 +12994,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12959,14 +13004,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46189</v>
+        <v>44989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12978,13 +13023,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13027,7 +13067,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 47902-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13041,10 +13081,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44676</v>
+        <v>45204</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13057,7 +13097,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13100,7 +13140,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13114,10 +13154,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46126</v>
+        <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13130,7 +13170,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13173,7 +13213,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13187,10 +13227,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44624</v>
+        <v>44712</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13203,7 +13243,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13246,7 +13286,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13260,10 +13300,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46191</v>
+        <v>45093</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13275,13 +13315,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13324,7 +13359,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13338,10 +13373,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45554</v>
+        <v>44624</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13354,7 +13389,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13397,7 +13432,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13411,10 +13446,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45523</v>
+        <v>45069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13427,7 +13462,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13470,7 +13505,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13480,14 +13515,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45523</v>
+        <v>46256</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13499,8 +13534,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13543,7 +13583,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13553,14 +13593,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46195</v>
+        <v>46256</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13578,7 +13618,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13621,7 +13661,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13635,10 +13675,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45153</v>
+        <v>46256</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13656,7 +13696,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13699,7 +13739,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13713,10 +13753,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45666</v>
+        <v>46256</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13728,8 +13768,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13772,7 +13817,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13786,10 +13831,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45113</v>
+        <v>44848</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13802,7 +13847,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13845,7 +13890,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13859,10 +13904,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46197</v>
+        <v>44676</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13875,7 +13920,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13918,7 +13963,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13932,10 +13977,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46197</v>
+        <v>46219</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13948,7 +13993,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13991,7 +14036,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14005,10 +14050,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44992</v>
+        <v>46219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14020,13 +14065,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14069,7 +14109,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14083,10 +14123,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46199</v>
+        <v>45421</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14098,13 +14138,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14147,7 +14182,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14161,10 +14196,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46199</v>
+        <v>46219</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14176,13 +14211,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14225,7 +14255,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14239,10 +14269,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46199</v>
+        <v>46222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14254,13 +14284,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14303,7 +14328,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14317,10 +14342,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44712</v>
+        <v>45438</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14333,7 +14358,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14376,7 +14401,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14390,10 +14415,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46202</v>
+        <v>45730</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14407,11 +14432,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14454,7 +14479,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14468,10 +14493,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45616</v>
+        <v>44764</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14484,7 +14509,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14527,7 +14552,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14541,10 +14566,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14562,7 +14587,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14605,7 +14630,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14619,10 +14644,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45043</v>
+        <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14634,8 +14659,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14678,7 +14708,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14692,10 +14722,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45483</v>
+        <v>46273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14707,8 +14737,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14751,7 +14786,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14765,10 +14800,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44988</v>
+        <v>46273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14786,7 +14821,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14829,7 +14864,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14843,10 +14878,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44804</v>
+        <v>46273</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14858,8 +14893,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14902,7 +14942,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14916,10 +14956,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45069</v>
+        <v>46273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14931,8 +14971,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14975,7 +15020,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14989,10 +15034,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45163</v>
+        <v>45337</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15005,7 +15050,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15048,7 +15093,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15062,10 +15107,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45762</v>
+        <v>46274</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15078,7 +15123,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15121,7 +15166,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15135,10 +15180,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45056</v>
+        <v>46230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15151,7 +15196,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15194,7 +15239,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15208,10 +15253,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45553</v>
+        <v>45421</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15223,13 +15268,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15272,7 +15312,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15286,10 +15326,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15307,7 +15347,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15350,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15364,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45646</v>
+        <v>46273</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15379,8 +15419,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15423,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15433,14 +15478,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45334</v>
+        <v>46230</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15453,7 +15498,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15496,7 +15541,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15510,10 +15555,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15531,7 +15576,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15574,7 +15619,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15588,10 +15633,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15609,7 +15654,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>8.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15652,7 +15697,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15662,14 +15707,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15687,7 +15732,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15730,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 36996-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15740,14 +15785,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15765,7 +15810,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15808,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 36997-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15822,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44950</v>
+        <v>46273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15837,8 +15882,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15881,7 +15931,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15895,10 +15945,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46219</v>
+        <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15910,8 +15960,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15954,7 +16009,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 38008-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15968,10 +16023,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46219</v>
+        <v>46280</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15983,8 +16038,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16027,7 +16087,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 38021-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16041,10 +16101,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46219</v>
+        <v>46280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16056,8 +16116,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16100,7 +16165,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16114,10 +16179,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46222</v>
+        <v>45540</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16130,7 +16195,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16173,7 +16238,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16187,10 +16252,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45601</v>
+        <v>45523</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16203,7 +16268,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16246,7 +16311,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16260,10 +16325,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44589</v>
+        <v>45523</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16276,7 +16341,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16319,7 +16384,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16333,10 +16398,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46273</v>
+        <v>45331</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16348,13 +16413,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16397,7 +16457,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16411,10 +16471,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44748</v>
+        <v>44998</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16427,7 +16487,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16470,7 +16530,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16484,10 +16544,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46273</v>
+        <v>44950</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16499,13 +16559,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16548,7 +16603,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16562,10 +16617,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46273</v>
+        <v>44992</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16583,7 +16638,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16626,7 +16681,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16640,10 +16695,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46273</v>
+        <v>46244</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16661,7 +16716,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16704,7 +16759,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16718,10 +16773,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46273</v>
+        <v>45056</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16733,13 +16788,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16782,7 +16832,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16796,10 +16846,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46273</v>
+        <v>44937</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16811,13 +16861,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16860,7 +16905,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16874,10 +16919,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46273</v>
+        <v>45281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16889,13 +16934,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16938,7 +16978,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16952,10 +16992,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46273</v>
+        <v>45560</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16967,13 +17007,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17016,7 +17051,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17030,10 +17065,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46230</v>
+        <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17046,7 +17081,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17089,7 +17124,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17103,10 +17138,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46273</v>
+        <v>45001</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17118,13 +17153,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17167,7 +17197,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 36996-2026</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17181,10 +17211,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46273</v>
+        <v>44988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17202,7 +17232,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17245,7 +17275,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 36997-2026</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17259,10 +17289,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46273</v>
+        <v>45309</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17274,13 +17304,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17323,7 +17348,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17337,10 +17362,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46273</v>
+        <v>45762</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17352,13 +17377,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17401,7 +17421,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17415,10 +17435,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46230</v>
+        <v>45553</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17430,8 +17450,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17474,7 +17499,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17488,10 +17513,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17509,7 +17534,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17552,7 +17577,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17566,10 +17591,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46273</v>
+        <v>45241</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17581,13 +17606,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17630,7 +17650,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17640,14 +17660,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45112</v>
+        <v>45014</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17659,13 +17679,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>12.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17708,7 +17723,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17722,10 +17737,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46274</v>
+        <v>45068</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17738,7 +17753,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17781,7 +17796,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17795,10 +17810,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45553</v>
+        <v>45068</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17810,13 +17825,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>4.6</v>
+        <v>0.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17859,7 +17869,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38021-2026</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17873,10 +17883,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46280</v>
+        <v>45616</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17888,13 +17898,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17937,7 +17942,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38008-2026</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17947,14 +17952,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46280</v>
+        <v>44986</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17966,13 +17971,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>12.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18015,7 +18015,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 61470-2024</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18029,10 +18029,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45646</v>
+        <v>45601</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18088,7 +18088,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18102,10 +18102,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45670</v>
+        <v>45174</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18166,7 +18166,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18180,10 +18180,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46244</v>
+        <v>45672</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18195,13 +18195,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18244,7 +18239,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18258,10 +18253,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45656</v>
+        <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18274,7 +18269,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18317,7 +18312,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 61470-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18331,10 +18326,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45600</v>
+        <v>45646</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18347,7 +18342,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18390,7 +18385,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 33334-2023</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18404,10 +18399,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45128</v>
+        <v>45656</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18420,7 +18415,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18463,7 +18458,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18477,10 +18472,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45622</v>
+        <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18493,7 +18488,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18536,7 +18531,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 10274-2023</t>
+          <t>A 33334-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18550,10 +18545,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44986</v>
+        <v>45128</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18566,7 +18561,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18609,7 +18604,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 58548-2024</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18623,10 +18618,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45635</v>
+        <v>45670</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18638,8 +18633,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>6.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18682,7 +18682,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 26863-2025</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18696,10 +18696,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45810</v>
+        <v>45622</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18772,7 +18772,7 @@
         <v>44889</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>44889</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>46256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46256</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>44746</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46189</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>44589</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45368</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44539</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46106</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45852</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44806</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45727</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>46052</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>46090</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45559</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45305</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>45042</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45447</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45362</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45656</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44601</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44656</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44519</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44508</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44734</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44609</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44830</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44632</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44488</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44748</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44593</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44843</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45483</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44839</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45553</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>45093</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45056</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45250</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45397</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45263</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45635</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>46031</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45740</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44484</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>45911</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>45666</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45047</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>45810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>46090</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>46090</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45068</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>46101</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>46126</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45236</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45973</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45001</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45113</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44993</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45204</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44796</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>45085</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44824</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>46009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45559</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>46009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45270</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44479</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45553</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>46155</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45740</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45128</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45128</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46167</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45098</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45813</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44589</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45163</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>46182</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45342</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46189</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46189</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>46189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>46189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45047</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46191</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46190</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>46190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>46197</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>46199</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46199</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>46202</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>44989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45204</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>44712</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45093</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44624</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46256</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>46256</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>46256</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>46256</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44848</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44676</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>46219</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>46219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45421</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>46219</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>46222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45438</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45730</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44764</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>46273</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>46273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>46273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>46273</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>46273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45337</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>46274</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>46230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45421</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>46273</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46230</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>46273</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>46273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46273</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>46273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>46280</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>46280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>45540</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>45523</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45523</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45331</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44998</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>44950</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44992</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>46244</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45056</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44937</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45560</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45001</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>44988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45309</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45762</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45553</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45553</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45241</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45014</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45068</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45068</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45616</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44986</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45601</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45174</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45672</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45646</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45656</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45128</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45670</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45622</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44889</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>44889</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>46256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46256</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>44746</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46189</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>44589</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45368</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44539</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>46080</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46106</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45852</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44806</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45727</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>46052</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>46090</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45559</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45305</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>45918</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>45042</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45447</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45362</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45656</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44601</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44656</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44722</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44519</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44830</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44508</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44734</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>44609</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44830</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44632</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44488</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44748</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44593</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44843</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44609</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45483</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44839</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45553</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>45093</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45056</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45250</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45397</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44986</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45263</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45635</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>46031</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45740</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44484</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>45911</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>45666</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>46073</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45047</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>45810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>46090</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>46090</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45068</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>46101</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>45112</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>46126</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45236</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45973</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45001</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45113</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44993</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45204</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>45840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44796</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>45085</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44824</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44748</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>46009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45559</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>46009</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45270</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44479</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45553</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>46155</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45740</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45128</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45128</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>46167</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45098</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45813</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44589</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45163</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>46182</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45342</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46189</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>46189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46189</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>46189</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>46189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45047</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46191</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46190</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>46190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>46195</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>46197</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>46199</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>46199</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>46202</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44989</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>44989</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45204</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>44712</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45093</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44624</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46256</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>46256</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>46256</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>46256</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>44848</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44676</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>46219</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>46219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45421</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>46219</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>46222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45438</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45730</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44764</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>46273</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>46273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>46273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>46273</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>46273</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45337</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>46274</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>46230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45421</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>46273</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46230</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>46273</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>46273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46273</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>46273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>46280</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>46280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>45540</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>45523</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45523</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45331</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44998</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>44950</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44992</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>46244</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45056</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>44937</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45560</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45091</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45001</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>44988</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45309</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45762</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45553</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45553</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45241</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45014</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45068</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45068</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45616</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>44986</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45601</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45174</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45672</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45646</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45656</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45128</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45670</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45622</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44889</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>44889</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>46256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46256</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 28147-2022</t>
+          <t>A 27395-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44746</v>
+        <v>46189</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -749,23 +749,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -777,18 +782,134 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
       </c>
       <c r="T3" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Entita
+Grantaggsvamp
+Talltita
+Vedticka
+Spillkråka
+Tofsmes
+Smålom</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 28147-2022</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
         <v>15</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre hackspett
@@ -800,157 +921,36 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 27395-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>16</v>
-      </c>
-      <c r="U4" t="n">
-        <v>16</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Entita
-Grantaggsvamp
-Talltita
-Vedticka
-Spillkråka
-Tofsmes
-Smålom</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
         <v/>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>44589</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45368</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44539</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11278-2026</t>
+          <t>A 11637-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46080</v>
+        <v>45727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1977,23 +1977,28 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2005,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2014,801 +2019,796 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 35099-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 11278-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Entita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 11678-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 15523-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46106</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I18" t="n">
         <v>3.7</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Thymalus limbatus
 Vanlig flatbagge</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 35099-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45852</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27240-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Skogsödla</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 37012-2022</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>44806</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>3.9</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>10</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 37012-2022 FSC-klagomål mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 37012-2022 tillsynsbegäran.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 37012-2022 tillsynsbegäran mail.docx", "A 37012-2022")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 37012-2022 prioriterade fågelarter.docx", "A 37012-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 11678-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S 765-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11678-2024 artfynd.xlsx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11678-2024 karta.png", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11678-2024 georefererad karta.tif", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11678-2024 FSC-klagomål.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11678-2024 FSC-klagomål mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11678-2024 tillsynsbegäran.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11678-2024 tillsynsbegäran mail.docx", "A 11678-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 11637-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ask
 Rävticka</t>
         </is>
       </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11637-2025 artfynd.xlsx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11637-2025 karta.png", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11637-2025 georefererad karta.tif", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11637-2025 FSC-klagomål.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11637-2025 FSC-klagomål mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11637-2025 tillsynsbegäran.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11637-2025 tillsynsbegäran mail.docx", "A 11637-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S 765-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Rävticka</t>
-        </is>
-      </c>
       <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/S 765-2025 artfynd.xlsx", "S 765-2025")</f>
         <v/>
@@ -2858,7 +2858,7 @@
         <v>46052</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14353-2024</t>
+          <t>A 18382-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45393</v>
+        <v>45042</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3118,46 +3118,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33259-2023</t>
+          <t>A 41241-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45127</v>
+        <v>45559</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,17 +3187,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3227,42 +3227,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12550-2026</t>
+          <t>A 22580-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46090</v>
+        <v>45447</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3291,13 +3291,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3330,49 +3325,53 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12557-2026</t>
+          <t>A 12550-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3389,7 +3388,7 @@
         <v>46090</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,13 +3406,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3443,46 +3442,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12550-2026 artfynd.xlsx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12550-2026 karta.png", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12550-2026 georefererad karta.tif", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12550-2026 FSC-klagomål.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12550-2026 FSC-klagomål mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12550-2026 tillsynsbegäran.docx", "A 12550-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12550-2026 tillsynsbegäran mail.docx", "A 12550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41241-2024</t>
+          <t>A 12557-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3496,10 +3495,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45559</v>
+        <v>46090</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3511,17 +3510,22 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3536,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3552,42 +3556,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 41241-2024 artfynd.xlsx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 12557-2026 artfynd.xlsx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 41241-2024 karta.png", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 12557-2026 karta.png", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 41241-2024 georefererad karta.tif", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 12557-2026 georefererad karta.tif", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 41241-2024 FSC-klagomål.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 12557-2026 FSC-klagomål.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 41241-2024 FSC-klagomål mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 12557-2026 FSC-klagomål mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 41241-2024 tillsynsbegäran.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 12557-2026 tillsynsbegäran.docx", "A 12557-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 41241-2024 tillsynsbegäran mail.docx", "A 41241-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 12557-2026 tillsynsbegäran mail.docx", "A 12557-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1515-2024</t>
+          <t>A 9690-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3601,10 +3605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45305</v>
+        <v>45362</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3617,7 +3621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3661,42 +3665,42 @@
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
         <v/>
       </c>
       <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 44857-2025</t>
+          <t>A 14353-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3710,10 +3714,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45918</v>
+        <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3726,16 +3730,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3750,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3766,42 +3770,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 14353-2024 artfynd.xlsx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 14353-2024 karta.png", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 14353-2024 georefererad karta.tif", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 14353-2024 FSC-klagomål.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 14353-2024 FSC-klagomål mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 14353-2024 tillsynsbegäran.docx", "A 14353-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 14353-2024 tillsynsbegäran mail.docx", "A 14353-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18382-2023</t>
+          <t>A 44857-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3815,10 +3819,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45042</v>
+        <v>45918</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3831,17 +3835,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3855,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3867,46 +3871,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 18382-2023 artfynd.xlsx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 44857-2025 artfynd.xlsx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 18382-2023 karta.png", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 44857-2025 karta.png", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 18382-2023 georefererad karta.tif", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 44857-2025 georefererad karta.tif", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 18382-2023 FSC-klagomål.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 44857-2025 FSC-klagomål.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 18382-2023 FSC-klagomål mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 44857-2025 FSC-klagomål mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 18382-2023 tillsynsbegäran.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 44857-2025 tillsynsbegäran.docx", "A 44857-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 18382-2023 tillsynsbegäran mail.docx", "A 18382-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 44857-2025 tillsynsbegäran mail.docx", "A 44857-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22580-2024</t>
+          <t>A 33259-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3920,10 +3924,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45447</v>
+        <v>45127</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3936,7 +3940,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3969,53 +3973,49 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 22580-2024 artfynd.xlsx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 33259-2023 artfynd.xlsx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 22580-2024 karta.png", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 33259-2023 karta.png", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 22580-2024 georefererad karta.tif", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 33259-2023 georefererad karta.tif", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 22580-2024 FSC-klagomål.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 33259-2023 FSC-klagomål.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 22580-2024 FSC-klagomål mail.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 33259-2023 FSC-klagomål mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 22580-2024 tillsynsbegäran.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 33259-2023 tillsynsbegäran.docx", "A 33259-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 22580-2024 tillsynsbegäran mail.docx", "A 22580-2024")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 22580-2024 prioriterade fågelarter.docx", "A 22580-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 33259-2023 tillsynsbegäran mail.docx", "A 33259-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9690-2024</t>
+          <t>A 290-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45362</v>
+        <v>45656</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4085,46 +4085,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 9690-2024 artfynd.xlsx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 9690-2024 karta.png", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 9690-2024 georefererad karta.tif", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 9690-2024 FSC-klagomål.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 9690-2024 FSC-klagomål mail.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 9690-2024 tillsynsbegäran.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 9690-2024 tillsynsbegäran mail.docx", "A 9690-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 9690-2024 prioriterade fågelarter.docx", "A 9690-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 290-2025</t>
+          <t>A 1515-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4138,10 +4134,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45656</v>
+        <v>45305</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4154,13 +4150,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4194,35 +4190,39 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 290-2025 artfynd.xlsx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 1515-2024 artfynd.xlsx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 290-2025 karta.png", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 1515-2024 karta.png", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 290-2025 georefererad karta.tif", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 1515-2024 georefererad karta.tif", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 290-2025 FSC-klagomål.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 1515-2024 FSC-klagomål.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 290-2025 FSC-klagomål mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 1515-2024 FSC-klagomål mail.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 290-2025 tillsynsbegäran.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 1515-2024 tillsynsbegäran.docx", "A 1515-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 290-2025 tillsynsbegäran mail.docx", "A 290-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 1515-2024 tillsynsbegäran mail.docx", "A 1515-2024")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 1515-2024 prioriterade fågelarter.docx", "A 1515-2024")</f>
         <v/>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46052</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53299-2021</t>
+          <t>A 6468-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44467</v>
+        <v>44601</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4468,13 +4468,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4517,7 +4512,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6468-2022</t>
+          <t>A 14830-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4531,10 +4526,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44601</v>
+        <v>44656</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4547,7 +4542,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4590,7 +4585,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14830-2022</t>
+          <t>A 23751-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4604,10 +4599,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44656</v>
+        <v>44722</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4620,7 +4615,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4663,7 +4658,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23751-2022</t>
+          <t>A 64156-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4673,14 +4668,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44722</v>
+        <v>44510</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,8 +4687,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64156-2021</t>
+          <t>A 66778-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4746,14 +4746,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44510</v>
+        <v>44519</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,13 +4765,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4814,7 +4809,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 66778-2021</t>
+          <t>A 41967-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4828,10 +4823,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44519</v>
+        <v>44830</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4843,8 +4838,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41967-2022</t>
+          <t>A 63567-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44830</v>
+        <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4916,13 +4916,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4965,7 +4960,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63567-2021</t>
+          <t>A 2851-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4979,10 +4974,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44508</v>
+        <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4995,7 +4990,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5038,7 +5033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2851-2022</t>
+          <t>A 26052-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5052,10 +5047,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44581</v>
+        <v>44734</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5068,7 +5063,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5111,7 +5106,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26052-2022</t>
+          <t>A 8047-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5125,10 +5120,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44734</v>
+        <v>44609</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5141,7 +5136,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5184,7 +5179,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8047-2022</t>
+          <t>A 41977-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5198,10 +5193,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44609</v>
+        <v>44830</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5213,8 +5208,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5257,7 +5257,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41977-2022</t>
+          <t>A 11661-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44830</v>
+        <v>44632</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5286,13 +5286,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5335,7 +5330,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11661-2022</t>
+          <t>A 58380-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5349,10 +5344,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44632</v>
+        <v>44488</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5365,7 +5360,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5408,7 +5403,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58380-2021</t>
+          <t>A 28616-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5422,10 +5417,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44488</v>
+        <v>44748</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5438,7 +5433,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5481,7 +5476,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28616-2022</t>
+          <t>A 5043-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5495,10 +5490,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44748</v>
+        <v>44593</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5511,7 +5506,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5554,7 +5549,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5043-2022</t>
+          <t>A 45105-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5568,10 +5563,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44593</v>
+        <v>44843</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5584,7 +5579,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5627,7 +5622,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45105-2022</t>
+          <t>A 8050-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5641,10 +5636,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44843</v>
+        <v>44609</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5657,7 +5652,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5700,7 +5695,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8050-2022</t>
+          <t>A 41979-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5714,10 +5709,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44609</v>
+        <v>44830</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5729,8 +5724,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
         <v>44524</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41979-2022</t>
+          <t>A 40696-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44830</v>
+        <v>44824</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5875,13 +5875,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5924,7 +5919,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29444-2024</t>
+          <t>A 4467-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5938,10 +5933,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45483</v>
+        <v>44589</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5954,7 +5949,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5997,7 +5992,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44343-2022</t>
+          <t>A 1607-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6011,10 +6006,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44839</v>
+        <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6027,7 +6022,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6070,7 +6065,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39872-2024</t>
+          <t>A 11676-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6084,10 +6079,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45553</v>
+        <v>45373</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6099,13 +6094,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6148,7 +6138,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26702-2023</t>
+          <t>A 61492-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6162,10 +6152,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45093</v>
+        <v>44916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6178,7 +6168,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6221,7 +6211,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11676-2024</t>
+          <t>A 56267-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6235,10 +6225,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45373</v>
+        <v>44479</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6251,7 +6241,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6294,7 +6284,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21042-2023</t>
+          <t>A 62160-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6308,10 +6298,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45056</v>
+        <v>45656</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6324,7 +6314,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6367,7 +6357,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58935-2023</t>
+          <t>A 26763-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6377,14 +6367,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45250</v>
+        <v>45093</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6397,7 +6387,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6440,7 +6430,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14734-2024</t>
+          <t>A 61584-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6454,10 +6444,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45397</v>
+        <v>46002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6470,7 +6460,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6513,7 +6503,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10274-2023</t>
+          <t>A 34885-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6527,10 +6517,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44986</v>
+        <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6586,7 +6576,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61644-2023</t>
+          <t>A 61581-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6600,10 +6590,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45263</v>
+        <v>46002</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6616,7 +6606,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6659,7 +6649,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33963-2023</t>
+          <t>A 50104-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6673,10 +6663,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45134</v>
+        <v>45600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6689,7 +6679,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6732,7 +6722,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58548-2024</t>
+          <t>A 53910-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6746,10 +6736,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45635</v>
+        <v>45231</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6762,7 +6752,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6805,7 +6795,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5559-2024</t>
+          <t>A 33334-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6815,14 +6805,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45334</v>
+        <v>45128</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6835,7 +6825,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6878,7 +6868,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1217-2026</t>
+          <t>A 37450-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6892,10 +6882,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46031</v>
+        <v>45540</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6908,7 +6898,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6951,7 +6941,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14169-2025</t>
+          <t>A 55727-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6965,10 +6955,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45740</v>
+        <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6981,7 +6971,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7024,7 +7014,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18645-2023</t>
+          <t>A 20800-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7038,10 +7028,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45043</v>
+        <v>45438</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7054,7 +7044,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7097,7 +7087,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4467-2022</t>
+          <t>A 62939-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7111,10 +7101,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44589</v>
+        <v>46009</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7126,8 +7116,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7170,7 +7165,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58020-2021</t>
+          <t>A 10274-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7184,10 +7179,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44484</v>
+        <v>44986</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7200,7 +7195,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7243,7 +7238,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1599-2025</t>
+          <t>A 62961-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7257,10 +7252,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45670</v>
+        <v>46009</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7278,7 +7273,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>18.8</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7321,7 +7316,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6223-2026</t>
+          <t>A 39871-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7335,10 +7330,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46055</v>
+        <v>45553</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7350,8 +7345,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7394,7 +7394,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43621-2025</t>
+          <t>A 12961-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45911</v>
+        <v>45001</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7467,7 +7467,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1157-2025</t>
+          <t>A 62978-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45666</v>
+        <v>46009</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7496,8 +7496,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7540,7 +7545,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 53910-2023</t>
+          <t>A 58548-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7554,10 +7559,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45231</v>
+        <v>45635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7570,7 +7575,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7613,7 +7618,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40240-2024</t>
+          <t>A 41233-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7627,10 +7632,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45554</v>
+        <v>45559</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7643,7 +7648,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7686,7 +7691,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9933-2026</t>
+          <t>A 2175-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7700,10 +7705,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46073</v>
+        <v>45309</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7716,7 +7721,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7759,7 +7764,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19045-2023</t>
+          <t>A 26863-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7773,10 +7778,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45047</v>
+        <v>45810</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7789,7 +7794,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7832,7 +7837,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26863-2025</t>
+          <t>A 33963-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7846,10 +7851,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45810</v>
+        <v>45134</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7862,7 +7867,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7905,7 +7910,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12546-2026</t>
+          <t>A 38922-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7919,10 +7924,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46090</v>
+        <v>45163</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,13 +7939,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 12547-2026</t>
+          <t>A 43621-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46090</v>
+        <v>45911</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8012,13 +8012,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8061,7 +8056,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22323-2023</t>
+          <t>A 18274-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8071,14 +8066,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45068</v>
+        <v>45421</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8091,7 +8086,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8134,7 +8129,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14739-2026</t>
+          <t>A 12516-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8148,10 +8143,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46101</v>
+        <v>45730</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8163,8 +8158,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30747-2023</t>
+          <t>A 56282-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45112</v>
+        <v>45241</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8236,13 +8236,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8285,7 +8280,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30802-2023</t>
+          <t>A 1217-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8295,14 +8290,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45112</v>
+        <v>46031</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8314,13 +8309,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8363,7 +8353,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11794-2023</t>
+          <t>A 37042-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8377,10 +8367,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44994</v>
+        <v>45539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8393,7 +8383,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8436,7 +8426,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3643-2023</t>
+          <t>A 7202-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8450,10 +8440,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44950</v>
+        <v>44965</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8466,7 +8456,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8509,7 +8499,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 18325-2026</t>
+          <t>A 19044-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8523,10 +8513,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46126</v>
+        <v>45047</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8539,7 +8529,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8582,7 +8572,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 54959-2023</t>
+          <t>A 55842-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8596,10 +8586,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45236</v>
+        <v>45973</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8611,8 +8601,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8655,7 +8650,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55842-2025</t>
+          <t>A 19045-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8669,10 +8664,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45973</v>
+        <v>45047</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8684,13 +8679,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8733,7 +8723,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12961-2023</t>
+          <t>A 14169-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8747,10 +8737,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45001</v>
+        <v>45740</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8763,7 +8753,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8806,7 +8796,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31113-2023</t>
+          <t>A 10273-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8816,14 +8806,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45113</v>
+        <v>44986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8836,7 +8826,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8879,7 +8869,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11383-2023</t>
+          <t>A 26121-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8893,10 +8883,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44993</v>
+        <v>45091</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8952,7 +8942,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61492-2022</t>
+          <t>A 6101-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8966,10 +8956,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44916</v>
+        <v>45337</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8982,7 +8972,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9025,7 +9015,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39871-2024</t>
+          <t>A 2039-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9039,10 +9029,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45553</v>
+        <v>45672</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9052,11 +9042,6 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -9103,7 +9088,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47906-2023</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9113,14 +9098,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45204</v>
+        <v>45068</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9133,7 +9118,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9176,7 +9161,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38922-2023</t>
+          <t>A 21886-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9190,10 +9175,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45163</v>
+        <v>45068</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9206,7 +9191,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9249,7 +9234,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33204-2025</t>
+          <t>A 6223-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9263,10 +9248,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45840</v>
+        <v>46055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9279,7 +9264,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9322,7 +9307,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34885-2022</t>
+          <t>A 1599-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9336,10 +9321,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44796</v>
+        <v>45670</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9351,8 +9336,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.9</v>
+        <v>18.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9395,7 +9385,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24913-2023</t>
+          <t>A 44343-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9409,10 +9399,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45085</v>
+        <v>44839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9425,7 +9415,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9468,7 +9458,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61584-2025</t>
+          <t>A 11794-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9482,10 +9472,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>44994</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9498,7 +9488,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9541,7 +9531,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 40696-2022</t>
+          <t>A 27947-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9555,10 +9545,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44824</v>
+        <v>45098</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9571,7 +9561,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9614,7 +9604,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61581-2025</t>
+          <t>A 33336-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9628,10 +9618,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46002</v>
+        <v>45128</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9644,7 +9634,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9687,7 +9677,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28579-2022</t>
+          <t>A 33337-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9701,10 +9691,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44748</v>
+        <v>45128</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9717,7 +9707,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9760,7 +9750,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 62978-2025</t>
+          <t>A 58935-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9770,14 +9760,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46009</v>
+        <v>45250</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9789,13 +9779,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9838,7 +9823,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 41233-2024</t>
+          <t>A 9933-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9852,10 +9837,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45559</v>
+        <v>46073</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9868,7 +9853,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9911,7 +9896,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62939-2025</t>
+          <t>A 62841-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9925,10 +9910,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46009</v>
+        <v>45270</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9940,13 +9925,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9989,7 +9969,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62961-2025</t>
+          <t>A 58020-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10003,10 +9983,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46009</v>
+        <v>44484</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10018,13 +9998,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10067,7 +10042,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 33262-2023</t>
+          <t>A 12546-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10081,10 +10056,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45127</v>
+        <v>46090</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10096,8 +10071,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10140,7 +10120,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62841-2023</t>
+          <t>A 41551-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10154,10 +10134,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45270</v>
+        <v>45560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10170,7 +10150,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10213,7 +10193,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37042-2024</t>
+          <t>A 12547-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10227,10 +10207,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45539</v>
+        <v>46090</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10242,8 +10222,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10286,7 +10271,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 56267-2021</t>
+          <t>A 6843-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10300,10 +10285,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44479</v>
+        <v>45342</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10316,7 +10301,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10359,7 +10344,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39867-2024</t>
+          <t>A 14739-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10373,10 +10358,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45553</v>
+        <v>46101</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10388,13 +10373,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10437,7 +10417,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22473-2026</t>
+          <t>A 12140-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10451,10 +10431,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46155</v>
+        <v>44998</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10466,13 +10446,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10515,7 +10490,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19178-2025</t>
+          <t>A 22323-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10525,14 +10500,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45769</v>
+        <v>45068</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10545,7 +10520,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10588,7 +10563,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14176-2025</t>
+          <t>A 41350-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10602,10 +10577,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45740</v>
+        <v>45174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10617,8 +10592,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10661,7 +10641,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33336-2023</t>
+          <t>A 46877-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10675,10 +10655,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45128</v>
+        <v>44848</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10691,7 +10671,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10734,7 +10714,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 33337-2023</t>
+          <t>A 54959-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10748,10 +10728,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45128</v>
+        <v>45236</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10764,7 +10744,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10807,7 +10787,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23907-2026</t>
+          <t>A 18325-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10821,10 +10801,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46167</v>
+        <v>46126</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10837,7 +10817,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10880,7 +10860,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 27947-2023</t>
+          <t>A 10787-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10890,14 +10870,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45098</v>
+        <v>44989</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10910,7 +10890,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10953,7 +10933,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 27638-2025</t>
+          <t>A 10791-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10963,14 +10943,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45813</v>
+        <v>44989</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10983,7 +10963,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11026,7 +11006,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24920-2026</t>
+          <t>A 3602-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11040,10 +11020,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46174</v>
+        <v>44950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11056,7 +11036,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11099,7 +11079,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24922-2026</t>
+          <t>A 12963-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11113,10 +11093,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46174</v>
+        <v>45001</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11129,7 +11109,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11172,7 +11152,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36516-2023</t>
+          <t>A 14734-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11186,10 +11166,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45153</v>
+        <v>45397</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11201,13 +11181,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11250,7 +11225,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 4470-2022</t>
+          <t>A 33204-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11264,10 +11239,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44589</v>
+        <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11280,7 +11255,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11323,7 +11298,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 38955-2023</t>
+          <t>A 30754-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11337,10 +11312,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45163</v>
+        <v>44764</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11353,7 +11328,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11396,7 +11371,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26198-2026</t>
+          <t>A 5373-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11410,10 +11385,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46182</v>
+        <v>45331</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11426,7 +11401,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11469,7 +11444,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7202-2023</t>
+          <t>A 30747-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11483,10 +11458,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44965</v>
+        <v>45112</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11498,8 +11473,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11542,7 +11522,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6843-2024</t>
+          <t>A 14702-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11556,10 +11536,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45342</v>
+        <v>45014</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11572,7 +11552,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>12.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11615,7 +11595,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 27384-2026</t>
+          <t>A 61644-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11629,10 +11609,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46189</v>
+        <v>45263</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11644,13 +11624,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11693,7 +11668,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 27388-2026</t>
+          <t>A 18272-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11707,10 +11682,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46189</v>
+        <v>45421</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11722,13 +11697,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11771,7 +11741,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27391-2026</t>
+          <t>A 47906-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11781,14 +11751,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46189</v>
+        <v>45204</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11800,13 +11770,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11849,7 +11814,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 27492-2026</t>
+          <t>A 19178-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11863,10 +11828,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46189</v>
+        <v>45769</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11879,7 +11844,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11922,7 +11887,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27387-2026</t>
+          <t>A 22473-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11936,10 +11901,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46189</v>
+        <v>46155</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11957,7 +11922,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12000,7 +11965,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27390-2026</t>
+          <t>A 14176-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12014,10 +11979,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46189</v>
+        <v>45740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12029,13 +11994,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12078,7 +12038,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 19044-2023</t>
+          <t>A 24913-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12092,10 +12052,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45047</v>
+        <v>45085</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12108,7 +12068,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12151,7 +12111,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27940-2026</t>
+          <t>A 21042-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12165,10 +12125,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46191</v>
+        <v>45056</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12180,13 +12140,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12229,7 +12184,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 27575-2026</t>
+          <t>A 23907-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12243,10 +12198,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46190</v>
+        <v>46167</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12258,13 +12213,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12307,7 +12257,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 27577-2026</t>
+          <t>A 33262-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12321,10 +12271,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46190</v>
+        <v>45127</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12336,13 +12286,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12385,7 +12330,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28178-2026</t>
+          <t>A 24920-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12399,10 +12344,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12414,13 +12359,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12463,7 +12403,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28475-2026</t>
+          <t>A 24922-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12477,10 +12417,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46197</v>
+        <v>46174</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12493,7 +12433,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12536,7 +12476,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28477-2026</t>
+          <t>A 11383-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12550,10 +12490,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46197</v>
+        <v>44993</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12566,7 +12506,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12609,7 +12549,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28876-2026</t>
+          <t>A 47902-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12623,10 +12563,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46199</v>
+        <v>45204</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12638,13 +12578,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12687,7 +12622,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28874-2026</t>
+          <t>A 27638-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12701,10 +12636,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46199</v>
+        <v>45813</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12716,13 +12651,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12765,7 +12695,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28875-2026</t>
+          <t>A 26702-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12779,10 +12709,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46199</v>
+        <v>45093</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12794,13 +12724,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12843,7 +12768,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 29263-2026</t>
+          <t>A 64615-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12857,10 +12782,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46202</v>
+        <v>45281</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12872,13 +12797,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12921,7 +12841,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10787-2023</t>
+          <t>A 16914-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12931,14 +12851,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44989</v>
+        <v>44676</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12951,7 +12871,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12994,7 +12914,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10791-2023</t>
+          <t>A 10617-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13004,14 +12924,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44989</v>
+        <v>44624</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13024,7 +12944,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>7.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13067,7 +12987,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 47902-2023</t>
+          <t>A 40240-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13081,10 +13001,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45204</v>
+        <v>45554</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13097,7 +13017,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13140,7 +13060,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 36444-2022</t>
+          <t>A 26198-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13154,10 +13074,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44804</v>
+        <v>46182</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13170,7 +13090,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13213,7 +13133,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22137-2022</t>
+          <t>A 33907-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13227,10 +13147,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44712</v>
+        <v>45523</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13243,7 +13163,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13286,7 +13206,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 26763-2023</t>
+          <t>A 33910-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13300,10 +13220,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45093</v>
+        <v>45523</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13316,7 +13236,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13359,7 +13279,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 10617-2022</t>
+          <t>A 36516-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13373,10 +13293,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44624</v>
+        <v>45153</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13388,8 +13308,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13432,7 +13357,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22198-2023</t>
+          <t>A 1157-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13446,10 +13371,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45069</v>
+        <v>45666</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13462,7 +13387,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13505,7 +13430,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34649-2026</t>
+          <t>A 31113-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13515,14 +13440,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46256</v>
+        <v>45113</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13534,13 +13459,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13583,7 +13503,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34650-2026</t>
+          <t>A 27577-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13593,14 +13513,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46256</v>
+        <v>46190</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13618,7 +13538,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13661,7 +13581,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 34648-2026</t>
+          <t>A 11289-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13675,10 +13595,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46256</v>
+        <v>44992</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13696,7 +13616,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13739,7 +13659,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 34651-2026</t>
+          <t>A 27387-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13753,10 +13673,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46256</v>
+        <v>46189</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13774,7 +13694,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13817,7 +13737,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 46877-2022</t>
+          <t>A 27391-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13831,10 +13751,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44848</v>
+        <v>46189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13846,8 +13766,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13890,7 +13815,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16914-2022</t>
+          <t>A 27575-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13904,10 +13829,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44676</v>
+        <v>46190</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13919,8 +13844,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13963,7 +13893,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31359-2026</t>
+          <t>A 27384-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13977,10 +13907,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46219</v>
+        <v>46189</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13992,8 +13922,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14036,7 +13971,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31361-2026</t>
+          <t>A 27388-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14050,10 +13985,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46219</v>
+        <v>46189</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14065,8 +14000,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14109,7 +14049,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18274-2024</t>
+          <t>A 27492-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14123,10 +14063,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45421</v>
+        <v>46189</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14139,7 +14079,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>10.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14182,7 +14122,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31360-2026</t>
+          <t>A 27390-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14196,10 +14136,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46219</v>
+        <v>46189</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14211,8 +14151,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14255,7 +14200,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 31478-2026</t>
+          <t>A 27940-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14269,10 +14214,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46222</v>
+        <v>46191</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14284,8 +14229,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14328,7 +14278,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 20800-2024</t>
+          <t>A 22137-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14342,10 +14292,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45438</v>
+        <v>44712</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14358,7 +14308,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14401,7 +14351,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12516-2025</t>
+          <t>A 28178-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14415,10 +14365,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45730</v>
+        <v>46195</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14432,11 +14382,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14479,7 +14429,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30754-2022</t>
+          <t>A 54227-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14493,10 +14443,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44764</v>
+        <v>45616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14509,7 +14459,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>9.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14552,7 +14502,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 36991-2026</t>
+          <t>A 28477-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14566,10 +14516,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46273</v>
+        <v>46197</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14581,13 +14531,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14630,7 +14575,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36994-2026</t>
+          <t>A 28475-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14644,10 +14589,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46273</v>
+        <v>46197</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14659,13 +14604,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14708,7 +14648,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 36998-2026</t>
+          <t>A 39872-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14722,10 +14662,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14743,7 +14683,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14786,7 +14726,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36999-2026</t>
+          <t>A 18645-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14800,10 +14740,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46273</v>
+        <v>45043</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14815,13 +14755,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14864,7 +14799,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37001-2026</t>
+          <t>A 29444-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14878,10 +14813,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46273</v>
+        <v>45483</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14893,13 +14828,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14942,7 +14872,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37008-2026</t>
+          <t>A 28876-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14956,10 +14886,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46273</v>
+        <v>46199</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14977,7 +14907,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15020,7 +14950,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6101-2024</t>
+          <t>A 28874-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15034,10 +14964,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45337</v>
+        <v>46199</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15049,8 +14979,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15093,7 +15028,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37251-2026</t>
+          <t>A 10746-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15107,10 +15042,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46274</v>
+        <v>44988</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15122,8 +15057,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15166,7 +15106,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31814-2026</t>
+          <t>A 28875-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15180,10 +15120,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46230</v>
+        <v>46199</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15195,8 +15135,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15239,7 +15184,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 18272-2024</t>
+          <t>A 36444-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15253,10 +15198,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45421</v>
+        <v>44804</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15269,7 +15214,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15312,7 +15257,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 36992-2026</t>
+          <t>A 29263-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15326,10 +15271,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46273</v>
+        <v>46202</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15347,7 +15292,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15390,7 +15335,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 37003-2026</t>
+          <t>A 22198-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15404,10 +15349,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46273</v>
+        <v>45069</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15419,13 +15364,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15408,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 31816-2026</t>
+          <t>A 38955-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15482,10 +15422,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46230</v>
+        <v>45163</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15541,7 +15481,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37004-2026</t>
+          <t>A 18400-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15555,10 +15495,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46273</v>
+        <v>45762</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15570,13 +15510,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15619,7 +15554,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37005-2026</t>
+          <t>A 20344-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15633,10 +15568,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46273</v>
+        <v>45056</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15648,13 +15583,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15697,7 +15627,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37007-2026</t>
+          <t>A 39875-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15711,10 +15641,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15732,7 +15662,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15705,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 36996-2026</t>
+          <t>A 39878-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15719,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15810,7 +15740,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15783,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36997-2026</t>
+          <t>A 61314-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15797,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46273</v>
+        <v>45646</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15882,13 +15812,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15931,7 +15856,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37006-2026</t>
+          <t>A 5559-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15941,14 +15866,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46273</v>
+        <v>45334</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15960,13 +15885,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16009,7 +15929,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38008-2026</t>
+          <t>A 34648-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16023,10 +15943,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46280</v>
+        <v>46256</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16044,7 +15964,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16087,7 +16007,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38021-2026</t>
+          <t>A 34651-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16101,10 +16021,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46280</v>
+        <v>46256</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16122,7 +16042,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16165,7 +16085,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 37450-2024</t>
+          <t>A 3643-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16179,10 +16099,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45540</v>
+        <v>44950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16195,7 +16115,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16238,7 +16158,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 33907-2024</t>
+          <t>A 34649-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16248,14 +16168,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45523</v>
+        <v>46256</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16267,8 +16187,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16311,7 +16236,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 33910-2024</t>
+          <t>A 34650-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16321,14 +16246,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45523</v>
+        <v>46256</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16340,8 +16265,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16384,7 +16314,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 5373-2024</t>
+          <t>A 31360-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16398,10 +16328,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45331</v>
+        <v>46219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16414,7 +16344,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16457,7 +16387,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12140-2023</t>
+          <t>A 31359-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16471,10 +16401,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44998</v>
+        <v>46219</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16487,7 +16417,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16530,7 +16460,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 3602-2023</t>
+          <t>A 31361-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16544,10 +16474,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44950</v>
+        <v>46219</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16560,7 +16490,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16603,7 +16533,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 11289-2023</t>
+          <t>A 50405-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16617,10 +16547,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44992</v>
+        <v>45601</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16632,13 +16562,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16681,7 +16606,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32975-2026</t>
+          <t>A 31478-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16695,10 +16620,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46244</v>
+        <v>46222</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16710,13 +16635,8 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16759,7 +16679,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 20344-2023</t>
+          <t>A 4470-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16773,10 +16693,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45056</v>
+        <v>44589</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16789,7 +16709,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16832,7 +16752,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 1607-2023</t>
+          <t>A 28579-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16846,10 +16766,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44937</v>
+        <v>44748</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16862,7 +16782,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16905,7 +16825,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 64615-2023</t>
+          <t>A 30802-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16915,14 +16835,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45281</v>
+        <v>45112</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16934,8 +16854,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16978,7 +16903,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 41551-2024</t>
+          <t>A 36991-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16992,10 +16917,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45560</v>
+        <v>46273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17007,8 +16932,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17051,7 +16981,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 26121-2023</t>
+          <t>A 37005-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17065,10 +16995,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45091</v>
+        <v>46273</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17080,8 +17010,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17124,7 +17059,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 12963-2023</t>
+          <t>A 37007-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17138,10 +17073,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45001</v>
+        <v>46273</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17153,8 +17088,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17197,7 +17137,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 10746-2023</t>
+          <t>A 36994-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17211,10 +17151,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44988</v>
+        <v>46273</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17232,7 +17172,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17275,7 +17215,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 2175-2024</t>
+          <t>A 36998-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17289,10 +17229,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45309</v>
+        <v>46273</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17304,8 +17244,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17348,7 +17293,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 18400-2025</t>
+          <t>A 36999-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17362,10 +17307,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45762</v>
+        <v>46273</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17377,8 +17322,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17421,7 +17371,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 39875-2024</t>
+          <t>A 37001-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17435,10 +17385,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17456,7 +17406,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17499,7 +17449,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 39878-2024</t>
+          <t>A 37008-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17513,10 +17463,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45553</v>
+        <v>46273</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17534,7 +17484,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17577,7 +17527,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 56282-2023</t>
+          <t>A 31816-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17591,10 +17541,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45241</v>
+        <v>46230</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17607,7 +17557,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17650,7 +17600,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 14702-2023</t>
+          <t>A 36992-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17664,10 +17614,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45014</v>
+        <v>46273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17679,8 +17629,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>12.1</v>
+        <v>3.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17723,7 +17678,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 36996-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17737,10 +17692,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45068</v>
+        <v>46273</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17752,8 +17707,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17796,7 +17756,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 21886-2023</t>
+          <t>A 36997-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17810,10 +17770,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45068</v>
+        <v>46273</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17825,8 +17785,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17869,7 +17834,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 54227-2024</t>
+          <t>A 37004-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17883,10 +17848,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45616</v>
+        <v>46273</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17898,8 +17863,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17942,7 +17912,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10273-2023</t>
+          <t>A 39867-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17952,14 +17922,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44986</v>
+        <v>45553</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17971,8 +17941,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>12.8</v>
+        <v>4.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18015,7 +17990,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 50405-2024</t>
+          <t>A 31814-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18029,10 +18004,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45601</v>
+        <v>46230</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18045,7 +18020,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18088,7 +18063,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 41350-2023</t>
+          <t>A 37003-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18102,10 +18077,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45174</v>
+        <v>46273</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18119,11 +18094,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I220" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18166,7 +18141,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 2039-2025</t>
+          <t>A 37006-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18180,10 +18155,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45672</v>
+        <v>46273</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18195,8 +18170,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18239,7 +18219,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61314-2024</t>
+          <t>A 37251-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18253,10 +18233,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45646</v>
+        <v>46274</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18269,7 +18249,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18312,7 +18292,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 61470-2024</t>
+          <t>A 38021-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18326,10 +18306,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45646</v>
+        <v>46280</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18341,8 +18321,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18385,7 +18370,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 62160-2024</t>
+          <t>A 38008-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18399,10 +18384,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45656</v>
+        <v>46280</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18414,8 +18399,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18458,7 +18448,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 50104-2024</t>
+          <t>A 61470-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18472,10 +18462,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45600</v>
+        <v>45646</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18488,7 +18478,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18531,7 +18521,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 33334-2023</t>
+          <t>A 1574-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18545,10 +18535,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45128</v>
+        <v>45670</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18560,8 +18550,13 @@
           <t>LEKEBERG</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18604,7 +18599,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 1574-2025</t>
+          <t>A 32975-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18618,10 +18613,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45670</v>
+        <v>46244</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18635,11 +18630,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>9.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18682,7 +18677,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 55727-2024</t>
+          <t>A 40002-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18696,10 +18691,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45622</v>
+        <v>46293</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18712,7 +18707,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18772,7 +18767,7 @@
         <v>44889</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18850,7 +18845,7 @@
         <v>44889</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18928,7 +18923,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19006,7 +19001,7 @@
         <v>45762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19084,7 +19079,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19157,7 +19152,7 @@
         <v>46076</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19230,7 +19225,7 @@
         <v>46256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19308,7 +19303,7 @@
         <v>46256</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>

--- a/Översikt LEKEBERG.xlsx
+++ b/Översikt LEKEBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46155</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 27395-2026</t>
+          <t>A 28147-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46189</v>
+        <v>44746</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -749,28 +749,23 @@
           <t>LEKEBERG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -782,18 +777,139 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
       </c>
       <c r="T3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Mindre hackspett
+Nötkråka
+Ullticka
+Grön sköldmossa
+Hasselsopp
+Stubbspretmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+      <c r="AE3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 27395-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
         <v>16</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>16</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Entita
@@ -805,152 +921,36 @@
 Smålom</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27395-2026 artfynd.xlsx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27395-2026 karta.png", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27395-2026 georefererad karta.tif", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27395-2026 FSC-klagomål.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27395-2026 FSC-klagomål mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27395-2026 tillsynsbegäran.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27395-2026 tillsynsbegäran mail.docx", "A 27395-2026")</f>
         <v/>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27395-2026 prioriterade fågelarter.docx", "A 27395-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 28147-2022</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>44746</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LEKEBERG</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Mindre hackspett
-Nötkråka
-Ullticka
-Grön sköldmossa
-Hasselsopp
-Stubbspretmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 28147-2022 artfynd.xlsx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 28147-2022 karta.png", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 28147-2022 georefererad karta.tif", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 28147-2022 FSC-klagomål.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 28147-2022 FSC-klagomål mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 28147-2022 tillsynsbegäran.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 28147-2022 tillsynsbegäran mail.docx", "A 28147-2022")</f>
-        <v/>
-      </c>
-      <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 28147-2022 prioriterade fågelarter.docx", "A 28147-2022")</f>
         <v/>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>45566</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>46059</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>44589</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46219</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45985</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45368</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44539</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11637-2025</t>
+          <t>A 35099-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45727</v>
+        <v>45852</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1979,17 +1979,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>16.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2007,723 +2007,723 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 35099-2025 artfynd.xlsx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 35099-2025 karta.png", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 35099-2025 georefererad karta.tif", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 35099-2025 FSC-klagomål.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 35099-2025 FSC-klagomål mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 35099-2025 tillsynsbegäran.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 35099-2025 tillsynsbegäran mail.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 35099-2025 prioriterade fågelarter.docx", "A 35099-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 11278-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 11278-2026 artfynd.xlsx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 11278-2026 karta.png", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 11278-2026 georefererad karta.tif", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 11278-2026 FSC-klagomål.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 11278-2026 FSC-klagomål mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 11278-2026 tillsynsbegäran.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 11278-2026 tillsynsbegäran mail.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 11278-2026 prioriterade fågelarter.docx", "A 11278-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 15523-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Thymalus limbatus
+Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 15523-2026 artfynd.xlsx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 15523-2026 karta.png", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 15523-2026 georefererad karta.tif", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 15523-2026 FSC-klagomål.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 15523-2026 FSC-klagomål mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 15523-2026 tillsynsbegäran.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 15523-2026 tillsynsbegäran mail.docx", "A 15523-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27240-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 27240-2026 artfynd.xlsx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 27240-2026 karta.png", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 27240-2026 georefererad karta.tif", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 27240-2026 FSC-klagomål.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomålsmail/A 27240-2026 FSC-klagomål mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsyn/A 27240-2026 tillsynsbegäran.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/tillsynsmail/A 27240-2026 tillsynsbegäran mail.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/fåglar/A 27240-2026 prioriterade fågelarter.docx", "A 27240-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 37012-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44806</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LEKEBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/artfynd/A 37012-2022 artfynd.xlsx", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor/A 37012-2022 karta.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/kartor_geotiff/A 37012-2022 georefererad karta.tif", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/knärot/A 37012-2022 karta knärot.png", "A 37012-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1814/klagomål/A 37012-2022 FSC-klagomål.docx", "A 37012-2022")</f>
+        <v/>
+     